--- a/유주네 자산 현황.xlsx
+++ b/유주네 자산 현황.xlsx
@@ -10,7 +10,7 @@
   </sheets>
   <definedNames>
     <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'총 자산 현황'!$A$1:$G$5</definedName>
-    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'상세 자산'!$A$1:$H$117</definedName>
+    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'상세 자산'!$A$1:$H$119</definedName>
     <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'대출'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr/>
@@ -23,10 +23,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={194daafe-c919-4020-895d-2bf5a9abb96f}</author>
+    <author>tc={064ca76c-e36b-48c9-b690-3553563f8b37}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{194daafe-c919-4020-895d-2bf5a9abb96f}" ref="E1">
+    <comment authorId="0" xr:uid="{064ca76c-e36b-48c9-b690-3553563f8b37}" ref="E1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="75">
   <si>
     <t>날짜</t>
   </si>
@@ -222,13 +222,16 @@
     <t>이더리움</t>
   </si>
   <si>
-    <t>하이닉스</t>
-  </si>
-  <si>
     <t>SK하이닉스</t>
   </si>
   <si>
     <t>퇴직연금 IRP</t>
+  </si>
+  <si>
+    <t>KODEX SK하이닉스단일종목레버리지</t>
+  </si>
+  <si>
+    <t>TIGER 미국우주테크</t>
   </si>
   <si>
     <t>은행</t>
@@ -238,6 +241,18 @@
   </si>
   <si>
     <t>월납입금</t>
+  </si>
+  <si>
+    <t>27.1.19</t>
+  </si>
+  <si>
+    <t>26.7.29</t>
+  </si>
+  <si>
+    <t>26.10.11</t>
+  </si>
+  <si>
+    <t>26.7.15</t>
   </si>
   <si>
     <t>하나은행</t>
@@ -260,7 +275,7 @@
     <numFmt numFmtId="164" formatCode="[$₩-412]#,##0"/>
     <numFmt numFmtId="165" formatCode="yyyy. M. d"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -289,6 +304,12 @@
     <font>
       <sz val="9.0"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -333,8 +354,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4A86E8"/>
-        <bgColor rgb="FF4A86E8"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -350,7 +371,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border/>
     <border>
       <left style="thin">
@@ -377,11 +398,25 @@
         <color rgb="FF000000"/>
       </top>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="50">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -437,29 +472,39 @@
     <xf borderId="1" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -474,25 +519,26 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="5" fontId="5" numFmtId="164" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="5" fontId="6" numFmtId="164" xfId="0" applyFill="1" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -523,14 +569,14 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Yuna Jeon" id="{0c1bf3df-658b-4a0a-b553-d5e720e3e938}" providerId="google-sheets"/>
+  <x18tc:person displayName="Yuna Jeon" id="{0dec116a-832f-4355-b955-da2c0f599fa3}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" invalid="1" refreshOnLoad="1">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:H87" sheet="상세 자산"/>
+    <worksheetSource ref="A1:H119" sheet="상세 자산"/>
   </cacheSource>
   <cacheFields>
     <cacheField name="날짜" numFmtId="49">
@@ -538,6 +584,7 @@
         <s v="2026년 3월"/>
         <s v="2026년 4월"/>
         <s v="2026년 5월"/>
+        <s v="2026년 6월"/>
       </sharedItems>
     </cacheField>
     <cacheField name="자산종류" numFmtId="0">
@@ -577,9 +624,10 @@
         <s v="S&amp;P 500"/>
         <s v="비트코인"/>
         <s v="이더리움"/>
-        <s v="하이닉스"/>
         <s v="SK하이닉스"/>
         <s v="퇴직연금 IRP"/>
+        <s v="KODEX SK하이닉스단일종목레버리지"/>
+        <s v="TIGER 미국우주테크"/>
       </sharedItems>
     </cacheField>
     <cacheField name="금액" numFmtId="164">
@@ -661,10 +709,38 @@
         <n v="1.4863767E7"/>
         <n v="2986000.0"/>
         <n v="1964334.0"/>
+        <n v="3000000.0"/>
+        <n v="1.704E7"/>
+        <n v="3.40857E7"/>
+        <n v="840450.0"/>
+        <n v="3.515244E7"/>
+        <n v="3.1824066E7"/>
+        <n v="1.0111032E7"/>
+        <n v="1.7802E7"/>
+        <n v="529335.0"/>
+        <n v="1.458E7"/>
+        <n v="8847280.0"/>
+        <n v="2284365.0"/>
+        <n v="1943040.0"/>
+        <n v="5.408E7"/>
+        <n v="9600000.0"/>
+        <n v="5.2824E7"/>
+        <n v="7529600.0"/>
+        <n v="5.987082E7"/>
+        <n v="4.947712E7"/>
+        <n v="1065140.0"/>
+        <n v="3841946.0"/>
+        <n v="1976115.0"/>
+        <n v="1.3419E7"/>
+        <n v="6660780.0"/>
+        <n v="1.6410176E7"/>
+        <n v="1.5576227E7"/>
+        <n v="2889806.0"/>
+        <n v="1433695.0"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="수익률" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1">
+    <cacheField name="수익률">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1">
         <m/>
         <n v="0.3871"/>
         <n v="0.238"/>
@@ -724,6 +800,31 @@
         <n v="0.227"/>
         <n v="-0.1455"/>
         <n v="-0.2397"/>
+        <n v="0.5753"/>
+        <n v="-0.2151"/>
+        <n v="1.2826"/>
+        <n v="0.4435"/>
+        <n v="0.2268"/>
+        <n v="0.485"/>
+        <n v="-0.33"/>
+        <s v="-"/>
+        <n v="0.8148"/>
+        <n v="0.4261"/>
+        <n v="0.2649"/>
+        <n v="0.9938"/>
+        <n v="4.85"/>
+        <n v="0.2892"/>
+        <n v="0.65"/>
+        <n v="0.4348"/>
+        <n v="-0.2019"/>
+        <n v="0.2806"/>
+        <n v="0.0152"/>
+        <n v="4.0208"/>
+        <n v="0.1882"/>
+        <n v="0.1468"/>
+        <n v="0.2307"/>
+        <n v="-0.294"/>
+        <n v="-0.4446"/>
       </sharedItems>
     </cacheField>
     <cacheField name="목적" numFmtId="0">
@@ -756,13 +857,14 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="목적별 현황" cacheId="0" dataCaption="" rowGrandTotals="0" compact="0" compactData="0">
-  <location ref="A1:J5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A1:J6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields>
     <pivotField name="날짜" axis="axisRow" compact="0" numFmtId="49" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
       <items>
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
+        <item x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -808,6 +910,7 @@
         <item x="19"/>
         <item x="20"/>
         <item x="21"/>
+        <item x="22"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -890,6 +993,34 @@
         <item x="74"/>
         <item x="75"/>
         <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -954,6 +1085,31 @@
         <item x="56"/>
         <item x="57"/>
         <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1192,7 +1348,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="E1" dT="2026-03-11T05:13:53.00" personId="{0c1bf3df-658b-4a0a-b553-d5e720e3e938}" id="{194daafe-c919-4020-895d-2bf5a9abb96f}" done="0">
+  <x18tc:threadedComment ref="E1" dT="2026-03-11T05:13:53.00" personId="{0dec116a-832f-4355-b955-da2c0f599fa3}" id="{064ca76c-e36b-48c9-b690-3553563f8b37}" done="0">
     <x18tc:text xml:space="preserve">최근 실거래가-전세금11억</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1337,15 +1493,15 @@
       </c>
       <c r="B5" s="3">
         <f>sumifs('상세 자산'!E:E,'상세 자산'!A:A,'상세 자산'!A88,'상세 자산'!B:B,'상세 자산'!$B$2)+sumifs('상세 자산'!E:E,'상세 자산'!A:A,'상세 자산'!A88,'상세 자산'!B:B,'상세 자산'!$B$5)</f>
-        <v>177633670</v>
+        <v>150833670</v>
       </c>
       <c r="C5" s="3">
         <f>sumifs('상세 자산'!E:E,'상세 자산'!A:A,'상세 자산'!A88,'상세 자산'!B:B,'상세 자산'!$B$17)+sumifs('상세 자산'!E:E,'상세 자산'!A:A,'상세 자산'!A88,'상세 자산'!B:B,'상세 자산'!$B$28)</f>
-        <v>200073999</v>
+        <v>246234802</v>
       </c>
       <c r="D5" s="3">
         <f>sumifs('상세 자산'!E:E,'상세 자산'!A:A,'상세 자산'!A88,'상세 자산'!B:B,'상세 자산'!$B$9)</f>
-        <v>181925150</v>
+        <v>193839331</v>
       </c>
       <c r="E5" s="4">
         <f t="shared" si="1"/>
@@ -1357,11 +1513,11 @@
       </c>
       <c r="G5" s="3">
         <f t="shared" si="2"/>
-        <v>2410607805</v>
+        <v>2441882789</v>
       </c>
       <c r="H5" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>31274984</v>
       </c>
     </row>
   </sheetData>
@@ -3313,7 +3469,7 @@
         <v>41</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E77" s="13">
         <v>2.4466E7</v>
@@ -3417,7 +3573,7 @@
         <v>41</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E81" s="13">
         <v>3760950.0</v>
@@ -3650,7 +3806,7 @@
         <v>21</v>
       </c>
       <c r="E90" s="20">
-        <v>2900000.0</v>
+        <v>3000000.0</v>
       </c>
       <c r="F90" s="14"/>
       <c r="G90" s="15" t="s">
@@ -3674,7 +3830,7 @@
         <v>29</v>
       </c>
       <c r="E91" s="20">
-        <v>1.694E7</v>
+        <v>1.704E7</v>
       </c>
       <c r="F91" s="14"/>
       <c r="G91" s="16" t="s">
@@ -3698,7 +3854,7 @@
         <v>31</v>
       </c>
       <c r="E92" s="20">
-        <v>2500000.0</v>
+        <v>3000000.0</v>
       </c>
       <c r="F92" s="17"/>
       <c r="G92" s="18" t="s">
@@ -3746,10 +3902,10 @@
         <v>35</v>
       </c>
       <c r="E94" s="20">
-        <v>3.21255E7</v>
+        <v>3.40857E7</v>
       </c>
       <c r="F94" s="17">
-        <v>0.4848</v>
+        <v>0.5753</v>
       </c>
       <c r="G94" s="15" t="s">
         <v>36</v>
@@ -3772,10 +3928,10 @@
         <v>37</v>
       </c>
       <c r="E95" s="20">
-        <v>1123850.0</v>
-      </c>
-      <c r="F95" s="17">
-        <v>0.0496</v>
+        <v>840450.0</v>
+      </c>
+      <c r="F95" s="21">
+        <v>-0.2151</v>
       </c>
       <c r="G95" s="15" t="s">
         <v>36</v>
@@ -3798,10 +3954,10 @@
         <v>38</v>
       </c>
       <c r="E96" s="20">
-        <v>3.202656E7</v>
+        <v>3.515244E7</v>
       </c>
       <c r="F96" s="17">
-        <v>1.0797</v>
+        <v>1.2826</v>
       </c>
       <c r="G96" s="15" t="s">
         <v>36</v>
@@ -3824,10 +3980,10 @@
         <v>39</v>
       </c>
       <c r="E97" s="20">
-        <v>2.8945596E7</v>
+        <v>3.1824066E7</v>
       </c>
       <c r="F97" s="17">
-        <v>0.384</v>
+        <v>0.4435</v>
       </c>
       <c r="G97" s="15" t="s">
         <v>36</v>
@@ -3850,10 +4006,10 @@
         <v>40</v>
       </c>
       <c r="E98" s="20">
-        <v>8939871.0</v>
+        <v>1.0111032E7</v>
       </c>
       <c r="F98" s="17">
-        <v>0.1396</v>
+        <v>0.2268</v>
       </c>
       <c r="G98" s="15" t="s">
         <v>36</v>
@@ -3876,10 +4032,10 @@
         <v>60</v>
       </c>
       <c r="E99" s="20">
-        <v>1.4814E7</v>
+        <v>1.7802E7</v>
       </c>
       <c r="F99" s="17">
-        <v>0.2413</v>
+        <v>0.485</v>
       </c>
       <c r="G99" s="15" t="s">
         <v>22</v>
@@ -3893,23 +4049,25 @@
         <v>11</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D100" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="E100" s="20">
-        <v>2.76E7</v>
-      </c>
-      <c r="F100" s="17"/>
+        <v>529335.0</v>
+      </c>
+      <c r="F100" s="21">
+        <v>-0.33</v>
+      </c>
       <c r="G100" s="15" t="s">
         <v>22</v>
       </c>
       <c r="H100" s="12" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
     </row>
     <row r="101">
@@ -3925,10 +4083,12 @@
       <c r="D101" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E101" s="20">
-        <v>1.448E7</v>
-      </c>
-      <c r="F101" s="17"/>
+      <c r="E101" s="13">
+        <v>1.458E7</v>
+      </c>
+      <c r="F101" s="22" t="s">
+        <v>28</v>
+      </c>
       <c r="G101" s="15" t="s">
         <v>30</v>
       </c>
@@ -3949,11 +4109,11 @@
       <c r="D102" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E102" s="20">
-        <v>8008800.0</v>
+      <c r="E102" s="13">
+        <v>8847280.0</v>
       </c>
       <c r="F102" s="17">
-        <v>0.6428</v>
+        <v>0.8148</v>
       </c>
       <c r="G102" s="15" t="s">
         <v>47</v>
@@ -3975,11 +4135,11 @@
       <c r="D103" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E103" s="20">
-        <v>2195255.0</v>
+      <c r="E103" s="13">
+        <v>2284365.0</v>
       </c>
       <c r="F103" s="17">
-        <v>0.3704</v>
+        <v>0.4261</v>
       </c>
       <c r="G103" s="15" t="s">
         <v>47</v>
@@ -4001,11 +4161,11 @@
       <c r="D104" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E104" s="20">
-        <v>1882320.0</v>
+      <c r="E104" s="13">
+        <v>1943040.0</v>
       </c>
       <c r="F104" s="17">
-        <v>0.2254</v>
+        <v>0.2649</v>
       </c>
       <c r="G104" s="15" t="s">
         <v>47</v>
@@ -4027,11 +4187,11 @@
       <c r="D105" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E105" s="20">
-        <v>4.7996E7</v>
+      <c r="E105" s="13">
+        <v>5.408E7</v>
       </c>
       <c r="F105" s="17">
-        <v>0.7695</v>
+        <v>0.9938</v>
       </c>
       <c r="G105" s="15" t="s">
         <v>51</v>
@@ -4053,11 +4213,11 @@
       <c r="D106" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E106" s="20">
-        <v>8520000.0</v>
+      <c r="E106" s="13">
+        <v>9600000.0</v>
       </c>
       <c r="F106" s="17">
-        <v>4.192</v>
+        <v>4.85</v>
       </c>
       <c r="G106" s="15" t="s">
         <v>51</v>
@@ -4077,13 +4237,13 @@
         <v>41</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E107" s="20">
-        <v>2.4466E7</v>
+        <v>60</v>
+      </c>
+      <c r="E107" s="13">
+        <v>5.2824E7</v>
       </c>
       <c r="F107" s="17">
-        <v>0.6394</v>
+        <v>0.2892</v>
       </c>
       <c r="G107" s="15" t="s">
         <v>32</v>
@@ -4105,11 +4265,11 @@
       <c r="D108" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E108" s="20">
-        <v>6816000.0</v>
+      <c r="E108" s="13">
+        <v>7529600.0</v>
       </c>
       <c r="F108" s="17">
-        <v>0.4936</v>
+        <v>0.65</v>
       </c>
       <c r="G108" s="15" t="s">
         <v>36</v>
@@ -4131,11 +4291,11 @@
       <c r="D109" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E109" s="20">
-        <v>5.784264E7</v>
+      <c r="E109" s="13">
+        <v>5.987082E7</v>
       </c>
       <c r="F109" s="17">
-        <v>0.3862</v>
+        <v>0.4348</v>
       </c>
       <c r="G109" s="15" t="s">
         <v>36</v>
@@ -4157,11 +4317,11 @@
       <c r="D110" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E110" s="20">
-        <v>4.822965E7</v>
+      <c r="E110" s="13">
+        <v>4.947712E7</v>
       </c>
       <c r="F110" s="17">
-        <v>0.2567</v>
+        <v>0.2892</v>
       </c>
       <c r="G110" s="15" t="s">
         <v>36</v>
@@ -4181,13 +4341,13 @@
         <v>41</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E111" s="20">
-        <v>3760950.0</v>
-      </c>
-      <c r="F111" s="17">
-        <v>0.2536</v>
+        <v>63</v>
+      </c>
+      <c r="E111" s="13">
+        <v>1065140.0</v>
+      </c>
+      <c r="F111" s="21">
+        <v>-0.2019</v>
       </c>
       <c r="G111" s="15" t="s">
         <v>36</v>
@@ -4201,22 +4361,22 @@
         <v>11</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E112" s="20">
-        <v>1.1928E7</v>
+        <v>61</v>
+      </c>
+      <c r="E112" s="13">
+        <v>3841946.0</v>
       </c>
       <c r="F112" s="17">
-        <v>3.4699</v>
+        <v>0.2806</v>
       </c>
       <c r="G112" s="15" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="H112" s="12" t="s">
         <v>28</v>
@@ -4227,22 +4387,22 @@
         <v>11</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E113" s="20">
-        <v>6994680.0</v>
+        <v>63</v>
+      </c>
+      <c r="E113" s="13">
+        <v>1976115.0</v>
       </c>
       <c r="F113" s="17">
-        <v>0.3036</v>
+        <v>0.0152</v>
       </c>
       <c r="G113" s="15" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="H113" s="12" t="s">
         <v>28</v>
@@ -4259,13 +4419,13 @@
         <v>52</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E114" s="20">
-        <v>1.5569376E7</v>
+        <v>50</v>
+      </c>
+      <c r="E114" s="13">
+        <v>1.3419E7</v>
       </c>
       <c r="F114" s="17">
-        <v>0.1365</v>
+        <v>4.0208</v>
       </c>
       <c r="G114" s="15" t="s">
         <v>53</v>
@@ -4285,13 +4445,13 @@
         <v>52</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="E115" s="20">
-        <v>1.4863767E7</v>
+        <v>54</v>
+      </c>
+      <c r="E115" s="13">
+        <v>6660780.0</v>
       </c>
       <c r="F115" s="17">
-        <v>0.227</v>
+        <v>0.1882</v>
       </c>
       <c r="G115" s="15" t="s">
         <v>53</v>
@@ -4305,19 +4465,19 @@
         <v>11</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="C116" s="12" t="s">
         <v>52</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E116" s="20">
-        <v>2986000.0</v>
+        <v>55</v>
+      </c>
+      <c r="E116" s="13">
+        <v>1.6410176E7</v>
       </c>
       <c r="F116" s="17">
-        <v>-0.1455</v>
+        <v>0.1468</v>
       </c>
       <c r="G116" s="15" t="s">
         <v>53</v>
@@ -4331,19 +4491,19 @@
         <v>11</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="C117" s="12" t="s">
         <v>52</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E117" s="20">
-        <v>1964334.0</v>
+        <v>56</v>
+      </c>
+      <c r="E117" s="13">
+        <v>1.5576227E7</v>
       </c>
       <c r="F117" s="17">
-        <v>-0.2397</v>
+        <v>0.2307</v>
       </c>
       <c r="G117" s="15" t="s">
         <v>53</v>
@@ -4353,3547 +4513,3599 @@
       </c>
     </row>
     <row r="118">
-      <c r="E118" s="21"/>
-      <c r="G118" s="22"/>
+      <c r="A118" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B118" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E118" s="13">
+        <v>2889806.0</v>
+      </c>
+      <c r="F118" s="21">
+        <v>-0.294</v>
+      </c>
+      <c r="G118" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="H118" s="12" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="119">
-      <c r="E119" s="21"/>
-      <c r="G119" s="22"/>
+      <c r="A119" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B119" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D119" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E119" s="13">
+        <v>1433695.0</v>
+      </c>
+      <c r="F119" s="21">
+        <v>-0.4446</v>
+      </c>
+      <c r="G119" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="H119" s="12" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="120">
-      <c r="E120" s="21"/>
-      <c r="G120" s="22"/>
+      <c r="E120" s="23"/>
+      <c r="G120" s="24"/>
     </row>
     <row r="121">
-      <c r="E121" s="21"/>
-      <c r="G121" s="22"/>
+      <c r="E121" s="23"/>
+      <c r="G121" s="24"/>
     </row>
     <row r="122">
-      <c r="E122" s="21"/>
-      <c r="G122" s="22"/>
+      <c r="E122" s="23"/>
+      <c r="G122" s="24"/>
     </row>
     <row r="123">
-      <c r="E123" s="21"/>
-      <c r="G123" s="22"/>
+      <c r="E123" s="23"/>
+      <c r="G123" s="24"/>
     </row>
     <row r="124">
-      <c r="E124" s="21"/>
-      <c r="G124" s="22"/>
+      <c r="E124" s="23"/>
+      <c r="G124" s="24"/>
     </row>
     <row r="125">
-      <c r="E125" s="21"/>
-      <c r="G125" s="22"/>
+      <c r="E125" s="23"/>
+      <c r="G125" s="24"/>
     </row>
     <row r="126">
-      <c r="E126" s="21"/>
-      <c r="G126" s="22"/>
+      <c r="E126" s="23"/>
+      <c r="G126" s="24"/>
     </row>
     <row r="127">
-      <c r="E127" s="21"/>
-      <c r="G127" s="22"/>
+      <c r="E127" s="23"/>
+      <c r="G127" s="24"/>
     </row>
     <row r="128">
-      <c r="E128" s="21"/>
-      <c r="G128" s="22"/>
+      <c r="E128" s="23"/>
+      <c r="G128" s="24"/>
     </row>
     <row r="129">
-      <c r="E129" s="21"/>
-      <c r="G129" s="22"/>
+      <c r="E129" s="23"/>
+      <c r="G129" s="24"/>
     </row>
     <row r="130">
-      <c r="E130" s="21"/>
-      <c r="G130" s="22"/>
+      <c r="E130" s="23"/>
+      <c r="G130" s="24"/>
     </row>
     <row r="131">
-      <c r="E131" s="21"/>
-      <c r="G131" s="22"/>
+      <c r="E131" s="23"/>
+      <c r="G131" s="24"/>
     </row>
     <row r="132">
-      <c r="E132" s="21"/>
-      <c r="G132" s="22"/>
+      <c r="E132" s="23"/>
+      <c r="G132" s="24"/>
     </row>
     <row r="133">
-      <c r="E133" s="21"/>
-      <c r="G133" s="22"/>
+      <c r="E133" s="23"/>
+      <c r="G133" s="24"/>
     </row>
     <row r="134">
-      <c r="E134" s="21"/>
-      <c r="G134" s="22"/>
+      <c r="E134" s="23"/>
+      <c r="G134" s="24"/>
     </row>
     <row r="135">
-      <c r="E135" s="21"/>
-      <c r="G135" s="22"/>
+      <c r="E135" s="23"/>
+      <c r="G135" s="24"/>
     </row>
     <row r="136">
-      <c r="E136" s="21"/>
-      <c r="G136" s="22"/>
+      <c r="E136" s="23"/>
+      <c r="G136" s="24"/>
     </row>
     <row r="137">
-      <c r="E137" s="21"/>
-      <c r="G137" s="22"/>
+      <c r="E137" s="23"/>
+      <c r="G137" s="24"/>
     </row>
     <row r="138">
-      <c r="E138" s="21"/>
-      <c r="G138" s="22"/>
+      <c r="E138" s="23"/>
+      <c r="G138" s="24"/>
     </row>
     <row r="139">
-      <c r="E139" s="21"/>
-      <c r="G139" s="22"/>
+      <c r="E139" s="23"/>
+      <c r="G139" s="24"/>
     </row>
     <row r="140">
-      <c r="E140" s="21"/>
-      <c r="G140" s="22"/>
+      <c r="E140" s="23"/>
+      <c r="G140" s="24"/>
     </row>
     <row r="141">
-      <c r="E141" s="21"/>
-      <c r="G141" s="22"/>
+      <c r="E141" s="23"/>
+      <c r="G141" s="24"/>
     </row>
     <row r="142">
-      <c r="E142" s="21"/>
-      <c r="G142" s="22"/>
+      <c r="E142" s="23"/>
+      <c r="G142" s="24"/>
     </row>
     <row r="143">
-      <c r="E143" s="21"/>
-      <c r="G143" s="22"/>
+      <c r="E143" s="23"/>
+      <c r="G143" s="24"/>
     </row>
     <row r="144">
-      <c r="E144" s="21"/>
-      <c r="G144" s="22"/>
+      <c r="E144" s="23"/>
+      <c r="G144" s="24"/>
     </row>
     <row r="145">
-      <c r="E145" s="21"/>
-      <c r="G145" s="22"/>
+      <c r="E145" s="23"/>
+      <c r="G145" s="24"/>
     </row>
     <row r="146">
-      <c r="E146" s="21"/>
-      <c r="G146" s="22"/>
+      <c r="E146" s="23"/>
+      <c r="G146" s="24"/>
     </row>
     <row r="147">
-      <c r="E147" s="21"/>
-      <c r="G147" s="22"/>
+      <c r="E147" s="23"/>
+      <c r="G147" s="24"/>
     </row>
     <row r="148">
-      <c r="E148" s="21"/>
-      <c r="G148" s="22"/>
+      <c r="E148" s="23"/>
+      <c r="G148" s="24"/>
     </row>
     <row r="149">
-      <c r="E149" s="21"/>
-      <c r="G149" s="22"/>
+      <c r="E149" s="23"/>
+      <c r="G149" s="24"/>
     </row>
     <row r="150">
-      <c r="E150" s="21"/>
-      <c r="G150" s="22"/>
+      <c r="E150" s="23"/>
+      <c r="G150" s="24"/>
     </row>
     <row r="151">
-      <c r="E151" s="21"/>
-      <c r="G151" s="22"/>
+      <c r="E151" s="23"/>
+      <c r="G151" s="24"/>
     </row>
     <row r="152">
-      <c r="E152" s="21"/>
-      <c r="G152" s="22"/>
+      <c r="E152" s="23"/>
+      <c r="G152" s="24"/>
     </row>
     <row r="153">
-      <c r="E153" s="21"/>
-      <c r="G153" s="22"/>
+      <c r="E153" s="23"/>
+      <c r="G153" s="24"/>
     </row>
     <row r="154">
-      <c r="E154" s="21"/>
-      <c r="G154" s="22"/>
+      <c r="E154" s="23"/>
+      <c r="G154" s="24"/>
     </row>
     <row r="155">
-      <c r="E155" s="21"/>
-      <c r="G155" s="22"/>
+      <c r="E155" s="23"/>
+      <c r="G155" s="24"/>
     </row>
     <row r="156">
-      <c r="E156" s="21"/>
-      <c r="G156" s="22"/>
+      <c r="E156" s="23"/>
+      <c r="G156" s="24"/>
     </row>
     <row r="157">
-      <c r="E157" s="21"/>
-      <c r="G157" s="22"/>
+      <c r="E157" s="23"/>
+      <c r="G157" s="24"/>
     </row>
     <row r="158">
-      <c r="E158" s="21"/>
-      <c r="G158" s="22"/>
+      <c r="E158" s="23"/>
+      <c r="G158" s="24"/>
     </row>
     <row r="159">
-      <c r="E159" s="21"/>
-      <c r="G159" s="22"/>
+      <c r="E159" s="23"/>
+      <c r="G159" s="24"/>
     </row>
     <row r="160">
-      <c r="E160" s="21"/>
-      <c r="G160" s="22"/>
+      <c r="E160" s="23"/>
+      <c r="G160" s="24"/>
     </row>
     <row r="161">
-      <c r="E161" s="21"/>
-      <c r="G161" s="22"/>
+      <c r="E161" s="23"/>
+      <c r="G161" s="24"/>
     </row>
     <row r="162">
-      <c r="E162" s="21"/>
-      <c r="G162" s="22"/>
+      <c r="E162" s="23"/>
+      <c r="G162" s="24"/>
     </row>
     <row r="163">
-      <c r="E163" s="21"/>
-      <c r="G163" s="22"/>
+      <c r="E163" s="23"/>
+      <c r="G163" s="24"/>
     </row>
     <row r="164">
-      <c r="E164" s="21"/>
-      <c r="G164" s="22"/>
+      <c r="E164" s="23"/>
+      <c r="G164" s="24"/>
     </row>
     <row r="165">
-      <c r="E165" s="21"/>
-      <c r="G165" s="22"/>
+      <c r="E165" s="23"/>
+      <c r="G165" s="24"/>
     </row>
     <row r="166">
-      <c r="E166" s="21"/>
-      <c r="G166" s="22"/>
+      <c r="E166" s="23"/>
+      <c r="G166" s="24"/>
     </row>
     <row r="167">
-      <c r="E167" s="21"/>
-      <c r="G167" s="22"/>
+      <c r="E167" s="23"/>
+      <c r="G167" s="24"/>
     </row>
     <row r="168">
-      <c r="E168" s="21"/>
-      <c r="G168" s="22"/>
+      <c r="E168" s="23"/>
+      <c r="G168" s="24"/>
     </row>
     <row r="169">
-      <c r="E169" s="21"/>
-      <c r="G169" s="22"/>
+      <c r="E169" s="23"/>
+      <c r="G169" s="24"/>
     </row>
     <row r="170">
-      <c r="E170" s="21"/>
-      <c r="G170" s="22"/>
+      <c r="E170" s="23"/>
+      <c r="G170" s="24"/>
     </row>
     <row r="171">
-      <c r="E171" s="21"/>
-      <c r="G171" s="22"/>
+      <c r="E171" s="23"/>
+      <c r="G171" s="24"/>
     </row>
     <row r="172">
-      <c r="E172" s="21"/>
-      <c r="G172" s="22"/>
+      <c r="E172" s="23"/>
+      <c r="G172" s="24"/>
     </row>
     <row r="173">
-      <c r="E173" s="21"/>
-      <c r="G173" s="22"/>
+      <c r="E173" s="23"/>
+      <c r="G173" s="24"/>
     </row>
     <row r="174">
-      <c r="E174" s="21"/>
-      <c r="G174" s="22"/>
+      <c r="E174" s="23"/>
+      <c r="G174" s="24"/>
     </row>
     <row r="175">
-      <c r="E175" s="21"/>
-      <c r="G175" s="22"/>
+      <c r="E175" s="23"/>
+      <c r="G175" s="24"/>
     </row>
     <row r="176">
-      <c r="E176" s="21"/>
-      <c r="G176" s="22"/>
+      <c r="E176" s="23"/>
+      <c r="G176" s="24"/>
     </row>
     <row r="177">
-      <c r="E177" s="21"/>
-      <c r="G177" s="22"/>
+      <c r="E177" s="23"/>
+      <c r="G177" s="24"/>
     </row>
     <row r="178">
-      <c r="E178" s="21"/>
-      <c r="G178" s="22"/>
+      <c r="E178" s="23"/>
+      <c r="G178" s="24"/>
     </row>
     <row r="179">
-      <c r="E179" s="21"/>
-      <c r="G179" s="22"/>
+      <c r="E179" s="23"/>
+      <c r="G179" s="24"/>
     </row>
     <row r="180">
-      <c r="E180" s="21"/>
-      <c r="G180" s="22"/>
+      <c r="E180" s="23"/>
+      <c r="G180" s="24"/>
     </row>
     <row r="181">
-      <c r="E181" s="21"/>
-      <c r="G181" s="22"/>
+      <c r="E181" s="23"/>
+      <c r="G181" s="24"/>
     </row>
     <row r="182">
-      <c r="E182" s="21"/>
-      <c r="G182" s="22"/>
+      <c r="E182" s="23"/>
+      <c r="G182" s="24"/>
     </row>
     <row r="183">
-      <c r="E183" s="21"/>
-      <c r="G183" s="22"/>
+      <c r="E183" s="23"/>
+      <c r="G183" s="24"/>
     </row>
     <row r="184">
-      <c r="E184" s="21"/>
-      <c r="G184" s="22"/>
+      <c r="E184" s="23"/>
+      <c r="G184" s="24"/>
     </row>
     <row r="185">
-      <c r="E185" s="21"/>
-      <c r="G185" s="22"/>
+      <c r="E185" s="23"/>
+      <c r="G185" s="24"/>
     </row>
     <row r="186">
-      <c r="E186" s="21"/>
-      <c r="G186" s="22"/>
+      <c r="E186" s="23"/>
+      <c r="G186" s="24"/>
     </row>
     <row r="187">
-      <c r="E187" s="21"/>
-      <c r="G187" s="22"/>
+      <c r="E187" s="23"/>
+      <c r="G187" s="24"/>
     </row>
     <row r="188">
-      <c r="E188" s="21"/>
-      <c r="G188" s="22"/>
+      <c r="E188" s="23"/>
+      <c r="G188" s="24"/>
     </row>
     <row r="189">
-      <c r="E189" s="21"/>
-      <c r="G189" s="22"/>
+      <c r="E189" s="23"/>
+      <c r="G189" s="24"/>
     </row>
     <row r="190">
-      <c r="E190" s="21"/>
-      <c r="G190" s="22"/>
+      <c r="E190" s="23"/>
+      <c r="G190" s="24"/>
     </row>
     <row r="191">
-      <c r="E191" s="21"/>
-      <c r="G191" s="22"/>
+      <c r="E191" s="23"/>
+      <c r="G191" s="24"/>
     </row>
     <row r="192">
-      <c r="E192" s="21"/>
-      <c r="G192" s="22"/>
+      <c r="E192" s="23"/>
+      <c r="G192" s="24"/>
     </row>
     <row r="193">
-      <c r="E193" s="21"/>
-      <c r="G193" s="22"/>
+      <c r="E193" s="23"/>
+      <c r="G193" s="24"/>
     </row>
     <row r="194">
-      <c r="E194" s="21"/>
-      <c r="G194" s="22"/>
+      <c r="E194" s="23"/>
+      <c r="G194" s="24"/>
     </row>
     <row r="195">
-      <c r="E195" s="21"/>
-      <c r="G195" s="22"/>
+      <c r="E195" s="23"/>
+      <c r="G195" s="24"/>
     </row>
     <row r="196">
-      <c r="E196" s="21"/>
-      <c r="G196" s="22"/>
+      <c r="E196" s="23"/>
+      <c r="G196" s="24"/>
     </row>
     <row r="197">
-      <c r="E197" s="21"/>
-      <c r="G197" s="22"/>
+      <c r="E197" s="23"/>
+      <c r="G197" s="24"/>
     </row>
     <row r="198">
-      <c r="E198" s="21"/>
-      <c r="G198" s="22"/>
+      <c r="E198" s="23"/>
+      <c r="G198" s="24"/>
     </row>
     <row r="199">
-      <c r="E199" s="21"/>
-      <c r="G199" s="22"/>
+      <c r="E199" s="23"/>
+      <c r="G199" s="24"/>
     </row>
     <row r="200">
-      <c r="E200" s="21"/>
-      <c r="G200" s="22"/>
+      <c r="E200" s="23"/>
+      <c r="G200" s="24"/>
     </row>
     <row r="201">
-      <c r="E201" s="21"/>
-      <c r="G201" s="22"/>
+      <c r="E201" s="23"/>
+      <c r="G201" s="24"/>
     </row>
     <row r="202">
-      <c r="E202" s="21"/>
-      <c r="G202" s="22"/>
+      <c r="E202" s="23"/>
+      <c r="G202" s="24"/>
     </row>
     <row r="203">
-      <c r="E203" s="21"/>
-      <c r="G203" s="22"/>
+      <c r="E203" s="23"/>
+      <c r="G203" s="24"/>
     </row>
     <row r="204">
-      <c r="E204" s="21"/>
-      <c r="G204" s="22"/>
+      <c r="E204" s="23"/>
+      <c r="G204" s="24"/>
     </row>
     <row r="205">
-      <c r="E205" s="21"/>
-      <c r="G205" s="22"/>
+      <c r="E205" s="23"/>
+      <c r="G205" s="24"/>
     </row>
     <row r="206">
-      <c r="E206" s="21"/>
-      <c r="G206" s="22"/>
+      <c r="E206" s="23"/>
+      <c r="G206" s="24"/>
     </row>
     <row r="207">
-      <c r="E207" s="21"/>
-      <c r="G207" s="22"/>
+      <c r="E207" s="23"/>
+      <c r="G207" s="24"/>
     </row>
     <row r="208">
-      <c r="E208" s="21"/>
-      <c r="G208" s="22"/>
+      <c r="E208" s="23"/>
+      <c r="G208" s="24"/>
     </row>
     <row r="209">
-      <c r="E209" s="21"/>
-      <c r="G209" s="22"/>
+      <c r="E209" s="23"/>
+      <c r="G209" s="24"/>
     </row>
     <row r="210">
-      <c r="E210" s="21"/>
-      <c r="G210" s="22"/>
+      <c r="E210" s="23"/>
+      <c r="G210" s="24"/>
     </row>
     <row r="211">
-      <c r="E211" s="21"/>
-      <c r="G211" s="22"/>
+      <c r="E211" s="23"/>
+      <c r="G211" s="24"/>
     </row>
     <row r="212">
-      <c r="E212" s="21"/>
-      <c r="G212" s="22"/>
+      <c r="E212" s="23"/>
+      <c r="G212" s="24"/>
     </row>
     <row r="213">
-      <c r="E213" s="21"/>
-      <c r="G213" s="22"/>
+      <c r="E213" s="23"/>
+      <c r="G213" s="24"/>
     </row>
     <row r="214">
-      <c r="E214" s="21"/>
-      <c r="G214" s="22"/>
+      <c r="E214" s="23"/>
+      <c r="G214" s="24"/>
     </row>
     <row r="215">
-      <c r="E215" s="21"/>
-      <c r="G215" s="22"/>
+      <c r="E215" s="23"/>
+      <c r="G215" s="24"/>
     </row>
     <row r="216">
-      <c r="E216" s="21"/>
-      <c r="G216" s="22"/>
+      <c r="E216" s="23"/>
+      <c r="G216" s="24"/>
     </row>
     <row r="217">
-      <c r="E217" s="21"/>
-      <c r="G217" s="22"/>
+      <c r="E217" s="23"/>
+      <c r="G217" s="24"/>
     </row>
     <row r="218">
-      <c r="E218" s="21"/>
-      <c r="G218" s="22"/>
+      <c r="E218" s="23"/>
+      <c r="G218" s="24"/>
     </row>
     <row r="219">
-      <c r="E219" s="21"/>
-      <c r="G219" s="22"/>
+      <c r="E219" s="23"/>
+      <c r="G219" s="24"/>
     </row>
     <row r="220">
-      <c r="E220" s="21"/>
-      <c r="G220" s="22"/>
+      <c r="E220" s="23"/>
+      <c r="G220" s="24"/>
     </row>
     <row r="221">
-      <c r="E221" s="21"/>
-      <c r="G221" s="22"/>
+      <c r="E221" s="23"/>
+      <c r="G221" s="24"/>
     </row>
     <row r="222">
-      <c r="E222" s="21"/>
-      <c r="G222" s="22"/>
+      <c r="E222" s="23"/>
+      <c r="G222" s="24"/>
     </row>
     <row r="223">
-      <c r="E223" s="21"/>
-      <c r="G223" s="22"/>
+      <c r="E223" s="23"/>
+      <c r="G223" s="24"/>
     </row>
     <row r="224">
-      <c r="E224" s="21"/>
-      <c r="G224" s="22"/>
+      <c r="E224" s="23"/>
+      <c r="G224" s="24"/>
     </row>
     <row r="225">
-      <c r="E225" s="21"/>
-      <c r="G225" s="22"/>
+      <c r="E225" s="23"/>
+      <c r="G225" s="24"/>
     </row>
     <row r="226">
-      <c r="E226" s="21"/>
-      <c r="G226" s="22"/>
+      <c r="E226" s="23"/>
+      <c r="G226" s="24"/>
     </row>
     <row r="227">
-      <c r="E227" s="21"/>
-      <c r="G227" s="22"/>
+      <c r="E227" s="23"/>
+      <c r="G227" s="24"/>
     </row>
     <row r="228">
-      <c r="E228" s="21"/>
-      <c r="G228" s="22"/>
+      <c r="E228" s="23"/>
+      <c r="G228" s="24"/>
     </row>
     <row r="229">
-      <c r="E229" s="21"/>
-      <c r="G229" s="22"/>
+      <c r="E229" s="23"/>
+      <c r="G229" s="24"/>
     </row>
     <row r="230">
-      <c r="E230" s="21"/>
-      <c r="G230" s="22"/>
+      <c r="E230" s="23"/>
+      <c r="G230" s="24"/>
     </row>
     <row r="231">
-      <c r="E231" s="21"/>
-      <c r="G231" s="22"/>
+      <c r="E231" s="23"/>
+      <c r="G231" s="24"/>
     </row>
     <row r="232">
-      <c r="E232" s="21"/>
-      <c r="G232" s="22"/>
+      <c r="E232" s="23"/>
+      <c r="G232" s="24"/>
     </row>
     <row r="233">
-      <c r="E233" s="21"/>
-      <c r="G233" s="22"/>
+      <c r="E233" s="23"/>
+      <c r="G233" s="24"/>
     </row>
     <row r="234">
-      <c r="E234" s="21"/>
-      <c r="G234" s="22"/>
+      <c r="E234" s="23"/>
+      <c r="G234" s="24"/>
     </row>
     <row r="235">
-      <c r="E235" s="21"/>
-      <c r="G235" s="22"/>
+      <c r="E235" s="23"/>
+      <c r="G235" s="24"/>
     </row>
     <row r="236">
-      <c r="E236" s="21"/>
-      <c r="G236" s="22"/>
+      <c r="E236" s="23"/>
+      <c r="G236" s="24"/>
     </row>
     <row r="237">
-      <c r="E237" s="21"/>
-      <c r="G237" s="22"/>
+      <c r="E237" s="23"/>
+      <c r="G237" s="24"/>
     </row>
     <row r="238">
-      <c r="E238" s="21"/>
-      <c r="G238" s="22"/>
+      <c r="E238" s="23"/>
+      <c r="G238" s="24"/>
     </row>
     <row r="239">
-      <c r="E239" s="21"/>
-      <c r="G239" s="22"/>
+      <c r="E239" s="23"/>
+      <c r="G239" s="24"/>
     </row>
     <row r="240">
-      <c r="E240" s="21"/>
-      <c r="G240" s="22"/>
+      <c r="E240" s="23"/>
+      <c r="G240" s="24"/>
     </row>
     <row r="241">
-      <c r="E241" s="21"/>
-      <c r="G241" s="22"/>
+      <c r="E241" s="23"/>
+      <c r="G241" s="24"/>
     </row>
     <row r="242">
-      <c r="E242" s="21"/>
-      <c r="G242" s="22"/>
+      <c r="E242" s="23"/>
+      <c r="G242" s="24"/>
     </row>
     <row r="243">
-      <c r="E243" s="21"/>
-      <c r="G243" s="22"/>
+      <c r="E243" s="23"/>
+      <c r="G243" s="24"/>
     </row>
     <row r="244">
-      <c r="E244" s="21"/>
-      <c r="G244" s="22"/>
+      <c r="E244" s="23"/>
+      <c r="G244" s="24"/>
     </row>
     <row r="245">
-      <c r="E245" s="21"/>
-      <c r="G245" s="22"/>
+      <c r="E245" s="23"/>
+      <c r="G245" s="24"/>
     </row>
     <row r="246">
-      <c r="E246" s="21"/>
-      <c r="G246" s="22"/>
+      <c r="E246" s="23"/>
+      <c r="G246" s="24"/>
     </row>
     <row r="247">
-      <c r="E247" s="21"/>
-      <c r="G247" s="22"/>
+      <c r="E247" s="23"/>
+      <c r="G247" s="24"/>
     </row>
     <row r="248">
-      <c r="E248" s="21"/>
-      <c r="G248" s="22"/>
+      <c r="E248" s="23"/>
+      <c r="G248" s="24"/>
     </row>
     <row r="249">
-      <c r="E249" s="21"/>
-      <c r="G249" s="22"/>
+      <c r="E249" s="23"/>
+      <c r="G249" s="24"/>
     </row>
     <row r="250">
-      <c r="E250" s="21"/>
-      <c r="G250" s="22"/>
+      <c r="E250" s="23"/>
+      <c r="G250" s="24"/>
     </row>
     <row r="251">
-      <c r="E251" s="21"/>
-      <c r="G251" s="22"/>
+      <c r="E251" s="23"/>
+      <c r="G251" s="24"/>
     </row>
     <row r="252">
-      <c r="E252" s="21"/>
-      <c r="G252" s="22"/>
+      <c r="E252" s="23"/>
+      <c r="G252" s="24"/>
     </row>
     <row r="253">
-      <c r="E253" s="21"/>
-      <c r="G253" s="22"/>
+      <c r="E253" s="23"/>
+      <c r="G253" s="24"/>
     </row>
     <row r="254">
-      <c r="E254" s="21"/>
-      <c r="G254" s="22"/>
+      <c r="E254" s="23"/>
+      <c r="G254" s="24"/>
     </row>
     <row r="255">
-      <c r="E255" s="21"/>
-      <c r="G255" s="22"/>
+      <c r="E255" s="23"/>
+      <c r="G255" s="24"/>
     </row>
     <row r="256">
-      <c r="E256" s="21"/>
-      <c r="G256" s="22"/>
+      <c r="E256" s="23"/>
+      <c r="G256" s="24"/>
     </row>
     <row r="257">
-      <c r="E257" s="21"/>
-      <c r="G257" s="22"/>
+      <c r="E257" s="23"/>
+      <c r="G257" s="24"/>
     </row>
     <row r="258">
-      <c r="E258" s="21"/>
-      <c r="G258" s="22"/>
+      <c r="E258" s="23"/>
+      <c r="G258" s="24"/>
     </row>
     <row r="259">
-      <c r="E259" s="21"/>
-      <c r="G259" s="22"/>
+      <c r="E259" s="23"/>
+      <c r="G259" s="24"/>
     </row>
     <row r="260">
-      <c r="E260" s="21"/>
-      <c r="G260" s="22"/>
+      <c r="E260" s="23"/>
+      <c r="G260" s="24"/>
     </row>
     <row r="261">
-      <c r="E261" s="21"/>
-      <c r="G261" s="22"/>
+      <c r="E261" s="23"/>
+      <c r="G261" s="24"/>
     </row>
     <row r="262">
-      <c r="E262" s="21"/>
-      <c r="G262" s="22"/>
+      <c r="E262" s="23"/>
+      <c r="G262" s="24"/>
     </row>
     <row r="263">
-      <c r="E263" s="21"/>
-      <c r="G263" s="22"/>
+      <c r="E263" s="23"/>
+      <c r="G263" s="24"/>
     </row>
     <row r="264">
-      <c r="E264" s="21"/>
-      <c r="G264" s="22"/>
+      <c r="E264" s="23"/>
+      <c r="G264" s="24"/>
     </row>
     <row r="265">
-      <c r="E265" s="21"/>
-      <c r="G265" s="22"/>
+      <c r="E265" s="23"/>
+      <c r="G265" s="24"/>
     </row>
     <row r="266">
-      <c r="E266" s="21"/>
-      <c r="G266" s="22"/>
+      <c r="E266" s="23"/>
+      <c r="G266" s="24"/>
     </row>
     <row r="267">
-      <c r="E267" s="21"/>
-      <c r="G267" s="22"/>
+      <c r="E267" s="23"/>
+      <c r="G267" s="24"/>
     </row>
     <row r="268">
-      <c r="E268" s="21"/>
-      <c r="G268" s="22"/>
+      <c r="E268" s="23"/>
+      <c r="G268" s="24"/>
     </row>
     <row r="269">
-      <c r="E269" s="21"/>
-      <c r="G269" s="22"/>
+      <c r="E269" s="23"/>
+      <c r="G269" s="24"/>
     </row>
     <row r="270">
-      <c r="E270" s="21"/>
-      <c r="G270" s="22"/>
+      <c r="E270" s="23"/>
+      <c r="G270" s="24"/>
     </row>
     <row r="271">
-      <c r="E271" s="21"/>
-      <c r="G271" s="22"/>
+      <c r="E271" s="23"/>
+      <c r="G271" s="24"/>
     </row>
     <row r="272">
-      <c r="E272" s="21"/>
-      <c r="G272" s="22"/>
+      <c r="E272" s="23"/>
+      <c r="G272" s="24"/>
     </row>
     <row r="273">
-      <c r="E273" s="21"/>
-      <c r="G273" s="22"/>
+      <c r="E273" s="23"/>
+      <c r="G273" s="24"/>
     </row>
     <row r="274">
-      <c r="E274" s="21"/>
-      <c r="G274" s="22"/>
+      <c r="E274" s="23"/>
+      <c r="G274" s="24"/>
     </row>
     <row r="275">
-      <c r="E275" s="21"/>
-      <c r="G275" s="22"/>
+      <c r="E275" s="23"/>
+      <c r="G275" s="24"/>
     </row>
     <row r="276">
-      <c r="E276" s="21"/>
-      <c r="G276" s="22"/>
+      <c r="E276" s="23"/>
+      <c r="G276" s="24"/>
     </row>
     <row r="277">
-      <c r="E277" s="21"/>
-      <c r="G277" s="22"/>
+      <c r="E277" s="23"/>
+      <c r="G277" s="24"/>
     </row>
     <row r="278">
-      <c r="E278" s="21"/>
-      <c r="G278" s="22"/>
+      <c r="E278" s="23"/>
+      <c r="G278" s="24"/>
     </row>
     <row r="279">
-      <c r="E279" s="21"/>
-      <c r="G279" s="22"/>
+      <c r="E279" s="23"/>
+      <c r="G279" s="24"/>
     </row>
     <row r="280">
-      <c r="E280" s="21"/>
-      <c r="G280" s="22"/>
+      <c r="E280" s="23"/>
+      <c r="G280" s="24"/>
     </row>
     <row r="281">
-      <c r="E281" s="21"/>
-      <c r="G281" s="22"/>
+      <c r="E281" s="23"/>
+      <c r="G281" s="24"/>
     </row>
     <row r="282">
-      <c r="E282" s="21"/>
-      <c r="G282" s="22"/>
+      <c r="E282" s="23"/>
+      <c r="G282" s="24"/>
     </row>
     <row r="283">
-      <c r="E283" s="21"/>
-      <c r="G283" s="22"/>
+      <c r="E283" s="23"/>
+      <c r="G283" s="24"/>
     </row>
     <row r="284">
-      <c r="E284" s="21"/>
-      <c r="G284" s="22"/>
+      <c r="E284" s="23"/>
+      <c r="G284" s="24"/>
     </row>
     <row r="285">
-      <c r="E285" s="21"/>
-      <c r="G285" s="22"/>
+      <c r="E285" s="23"/>
+      <c r="G285" s="24"/>
     </row>
     <row r="286">
-      <c r="E286" s="21"/>
-      <c r="G286" s="22"/>
+      <c r="E286" s="23"/>
+      <c r="G286" s="24"/>
     </row>
     <row r="287">
-      <c r="E287" s="21"/>
-      <c r="G287" s="22"/>
+      <c r="E287" s="23"/>
+      <c r="G287" s="24"/>
     </row>
     <row r="288">
-      <c r="E288" s="21"/>
-      <c r="G288" s="22"/>
+      <c r="E288" s="23"/>
+      <c r="G288" s="24"/>
     </row>
     <row r="289">
-      <c r="E289" s="21"/>
-      <c r="G289" s="22"/>
+      <c r="E289" s="23"/>
+      <c r="G289" s="24"/>
     </row>
     <row r="290">
-      <c r="E290" s="21"/>
-      <c r="G290" s="22"/>
+      <c r="E290" s="23"/>
+      <c r="G290" s="24"/>
     </row>
     <row r="291">
-      <c r="E291" s="21"/>
-      <c r="G291" s="22"/>
+      <c r="E291" s="23"/>
+      <c r="G291" s="24"/>
     </row>
     <row r="292">
-      <c r="E292" s="21"/>
-      <c r="G292" s="22"/>
+      <c r="E292" s="23"/>
+      <c r="G292" s="24"/>
     </row>
     <row r="293">
-      <c r="E293" s="21"/>
-      <c r="G293" s="22"/>
+      <c r="E293" s="23"/>
+      <c r="G293" s="24"/>
     </row>
     <row r="294">
-      <c r="E294" s="21"/>
-      <c r="G294" s="22"/>
+      <c r="E294" s="23"/>
+      <c r="G294" s="24"/>
     </row>
     <row r="295">
-      <c r="E295" s="21"/>
-      <c r="G295" s="22"/>
+      <c r="E295" s="23"/>
+      <c r="G295" s="24"/>
     </row>
     <row r="296">
-      <c r="E296" s="21"/>
-      <c r="G296" s="22"/>
+      <c r="E296" s="23"/>
+      <c r="G296" s="24"/>
     </row>
     <row r="297">
-      <c r="E297" s="21"/>
-      <c r="G297" s="22"/>
+      <c r="E297" s="23"/>
+      <c r="G297" s="24"/>
     </row>
     <row r="298">
-      <c r="E298" s="21"/>
-      <c r="G298" s="22"/>
+      <c r="E298" s="23"/>
+      <c r="G298" s="24"/>
     </row>
     <row r="299">
-      <c r="E299" s="21"/>
-      <c r="G299" s="22"/>
+      <c r="E299" s="23"/>
+      <c r="G299" s="24"/>
     </row>
     <row r="300">
-      <c r="E300" s="21"/>
-      <c r="G300" s="22"/>
+      <c r="E300" s="23"/>
+      <c r="G300" s="24"/>
     </row>
     <row r="301">
-      <c r="E301" s="21"/>
-      <c r="G301" s="22"/>
+      <c r="E301" s="23"/>
+      <c r="G301" s="24"/>
     </row>
     <row r="302">
-      <c r="E302" s="21"/>
-      <c r="G302" s="22"/>
+      <c r="E302" s="23"/>
+      <c r="G302" s="24"/>
     </row>
     <row r="303">
-      <c r="E303" s="21"/>
-      <c r="G303" s="22"/>
+      <c r="E303" s="23"/>
+      <c r="G303" s="24"/>
     </row>
     <row r="304">
-      <c r="E304" s="21"/>
-      <c r="G304" s="22"/>
+      <c r="E304" s="23"/>
+      <c r="G304" s="24"/>
     </row>
     <row r="305">
-      <c r="E305" s="21"/>
-      <c r="G305" s="22"/>
+      <c r="E305" s="23"/>
+      <c r="G305" s="24"/>
     </row>
     <row r="306">
-      <c r="E306" s="21"/>
-      <c r="G306" s="22"/>
+      <c r="E306" s="23"/>
+      <c r="G306" s="24"/>
     </row>
     <row r="307">
-      <c r="E307" s="21"/>
-      <c r="G307" s="22"/>
+      <c r="E307" s="23"/>
+      <c r="G307" s="24"/>
     </row>
     <row r="308">
-      <c r="E308" s="21"/>
-      <c r="G308" s="22"/>
+      <c r="E308" s="23"/>
+      <c r="G308" s="24"/>
     </row>
     <row r="309">
-      <c r="E309" s="21"/>
-      <c r="G309" s="22"/>
+      <c r="E309" s="23"/>
+      <c r="G309" s="24"/>
     </row>
     <row r="310">
-      <c r="E310" s="21"/>
-      <c r="G310" s="22"/>
+      <c r="E310" s="23"/>
+      <c r="G310" s="24"/>
     </row>
     <row r="311">
-      <c r="E311" s="21"/>
-      <c r="G311" s="22"/>
+      <c r="E311" s="23"/>
+      <c r="G311" s="24"/>
     </row>
     <row r="312">
-      <c r="E312" s="21"/>
-      <c r="G312" s="22"/>
+      <c r="E312" s="23"/>
+      <c r="G312" s="24"/>
     </row>
     <row r="313">
-      <c r="E313" s="21"/>
-      <c r="G313" s="22"/>
+      <c r="E313" s="23"/>
+      <c r="G313" s="24"/>
     </row>
     <row r="314">
-      <c r="E314" s="21"/>
-      <c r="G314" s="22"/>
+      <c r="E314" s="23"/>
+      <c r="G314" s="24"/>
     </row>
     <row r="315">
-      <c r="E315" s="21"/>
-      <c r="G315" s="22"/>
+      <c r="E315" s="23"/>
+      <c r="G315" s="24"/>
     </row>
     <row r="316">
-      <c r="E316" s="21"/>
-      <c r="G316" s="22"/>
+      <c r="E316" s="23"/>
+      <c r="G316" s="24"/>
     </row>
     <row r="317">
-      <c r="E317" s="21"/>
-      <c r="G317" s="22"/>
+      <c r="E317" s="23"/>
+      <c r="G317" s="24"/>
     </row>
     <row r="318">
-      <c r="E318" s="21"/>
-      <c r="G318" s="22"/>
+      <c r="E318" s="23"/>
+      <c r="G318" s="24"/>
     </row>
     <row r="319">
-      <c r="E319" s="21"/>
-      <c r="G319" s="22"/>
+      <c r="E319" s="23"/>
+      <c r="G319" s="24"/>
     </row>
     <row r="320">
-      <c r="E320" s="21"/>
-      <c r="G320" s="22"/>
+      <c r="E320" s="23"/>
+      <c r="G320" s="24"/>
     </row>
     <row r="321">
-      <c r="E321" s="21"/>
-      <c r="G321" s="22"/>
+      <c r="E321" s="23"/>
+      <c r="G321" s="24"/>
     </row>
     <row r="322">
-      <c r="E322" s="21"/>
-      <c r="G322" s="22"/>
+      <c r="E322" s="23"/>
+      <c r="G322" s="24"/>
     </row>
     <row r="323">
-      <c r="E323" s="21"/>
-      <c r="G323" s="22"/>
+      <c r="E323" s="23"/>
+      <c r="G323" s="24"/>
     </row>
     <row r="324">
-      <c r="E324" s="21"/>
-      <c r="G324" s="22"/>
+      <c r="E324" s="23"/>
+      <c r="G324" s="24"/>
     </row>
     <row r="325">
-      <c r="E325" s="21"/>
-      <c r="G325" s="22"/>
+      <c r="E325" s="23"/>
+      <c r="G325" s="24"/>
     </row>
     <row r="326">
-      <c r="E326" s="21"/>
-      <c r="G326" s="22"/>
+      <c r="E326" s="23"/>
+      <c r="G326" s="24"/>
     </row>
     <row r="327">
-      <c r="E327" s="21"/>
-      <c r="G327" s="22"/>
+      <c r="E327" s="23"/>
+      <c r="G327" s="24"/>
     </row>
     <row r="328">
-      <c r="E328" s="21"/>
-      <c r="G328" s="22"/>
+      <c r="E328" s="23"/>
+      <c r="G328" s="24"/>
     </row>
     <row r="329">
-      <c r="E329" s="21"/>
-      <c r="G329" s="22"/>
+      <c r="E329" s="23"/>
+      <c r="G329" s="24"/>
     </row>
     <row r="330">
-      <c r="E330" s="21"/>
-      <c r="G330" s="22"/>
+      <c r="E330" s="23"/>
+      <c r="G330" s="24"/>
     </row>
     <row r="331">
-      <c r="E331" s="21"/>
-      <c r="G331" s="22"/>
+      <c r="E331" s="23"/>
+      <c r="G331" s="24"/>
     </row>
     <row r="332">
-      <c r="E332" s="21"/>
-      <c r="G332" s="22"/>
+      <c r="E332" s="23"/>
+      <c r="G332" s="24"/>
     </row>
     <row r="333">
-      <c r="E333" s="21"/>
-      <c r="G333" s="22"/>
+      <c r="E333" s="23"/>
+      <c r="G333" s="24"/>
     </row>
     <row r="334">
-      <c r="E334" s="21"/>
-      <c r="G334" s="22"/>
+      <c r="E334" s="23"/>
+      <c r="G334" s="24"/>
     </row>
     <row r="335">
-      <c r="E335" s="21"/>
-      <c r="G335" s="22"/>
+      <c r="E335" s="23"/>
+      <c r="G335" s="24"/>
     </row>
     <row r="336">
-      <c r="E336" s="21"/>
-      <c r="G336" s="22"/>
+      <c r="E336" s="23"/>
+      <c r="G336" s="24"/>
     </row>
     <row r="337">
-      <c r="E337" s="21"/>
-      <c r="G337" s="22"/>
+      <c r="E337" s="23"/>
+      <c r="G337" s="24"/>
     </row>
     <row r="338">
-      <c r="E338" s="21"/>
-      <c r="G338" s="22"/>
+      <c r="E338" s="23"/>
+      <c r="G338" s="24"/>
     </row>
     <row r="339">
-      <c r="E339" s="21"/>
-      <c r="G339" s="22"/>
+      <c r="E339" s="23"/>
+      <c r="G339" s="24"/>
     </row>
     <row r="340">
-      <c r="E340" s="21"/>
-      <c r="G340" s="22"/>
+      <c r="E340" s="23"/>
+      <c r="G340" s="24"/>
     </row>
     <row r="341">
-      <c r="E341" s="21"/>
-      <c r="G341" s="22"/>
+      <c r="E341" s="23"/>
+      <c r="G341" s="24"/>
     </row>
     <row r="342">
-      <c r="E342" s="21"/>
-      <c r="G342" s="22"/>
+      <c r="E342" s="23"/>
+      <c r="G342" s="24"/>
     </row>
     <row r="343">
-      <c r="E343" s="21"/>
-      <c r="G343" s="22"/>
+      <c r="E343" s="23"/>
+      <c r="G343" s="24"/>
     </row>
     <row r="344">
-      <c r="E344" s="21"/>
-      <c r="G344" s="22"/>
+      <c r="E344" s="23"/>
+      <c r="G344" s="24"/>
     </row>
     <row r="345">
-      <c r="E345" s="21"/>
-      <c r="G345" s="22"/>
+      <c r="E345" s="23"/>
+      <c r="G345" s="24"/>
     </row>
     <row r="346">
-      <c r="E346" s="21"/>
-      <c r="G346" s="22"/>
+      <c r="E346" s="23"/>
+      <c r="G346" s="24"/>
     </row>
     <row r="347">
-      <c r="E347" s="21"/>
-      <c r="G347" s="22"/>
+      <c r="E347" s="23"/>
+      <c r="G347" s="24"/>
     </row>
     <row r="348">
-      <c r="E348" s="21"/>
-      <c r="G348" s="22"/>
+      <c r="E348" s="23"/>
+      <c r="G348" s="24"/>
     </row>
     <row r="349">
-      <c r="E349" s="21"/>
-      <c r="G349" s="22"/>
+      <c r="E349" s="23"/>
+      <c r="G349" s="24"/>
     </row>
     <row r="350">
-      <c r="E350" s="21"/>
-      <c r="G350" s="22"/>
+      <c r="E350" s="23"/>
+      <c r="G350" s="24"/>
     </row>
     <row r="351">
-      <c r="E351" s="21"/>
-      <c r="G351" s="22"/>
+      <c r="E351" s="23"/>
+      <c r="G351" s="24"/>
     </row>
     <row r="352">
-      <c r="E352" s="21"/>
-      <c r="G352" s="22"/>
+      <c r="E352" s="23"/>
+      <c r="G352" s="24"/>
     </row>
     <row r="353">
-      <c r="E353" s="21"/>
-      <c r="G353" s="22"/>
+      <c r="E353" s="23"/>
+      <c r="G353" s="24"/>
     </row>
     <row r="354">
-      <c r="E354" s="21"/>
-      <c r="G354" s="22"/>
+      <c r="E354" s="23"/>
+      <c r="G354" s="24"/>
     </row>
     <row r="355">
-      <c r="E355" s="21"/>
-      <c r="G355" s="22"/>
+      <c r="E355" s="23"/>
+      <c r="G355" s="24"/>
     </row>
     <row r="356">
-      <c r="E356" s="21"/>
-      <c r="G356" s="22"/>
+      <c r="E356" s="23"/>
+      <c r="G356" s="24"/>
     </row>
     <row r="357">
-      <c r="E357" s="21"/>
-      <c r="G357" s="22"/>
+      <c r="E357" s="23"/>
+      <c r="G357" s="24"/>
     </row>
     <row r="358">
-      <c r="E358" s="21"/>
-      <c r="G358" s="22"/>
+      <c r="E358" s="23"/>
+      <c r="G358" s="24"/>
     </row>
     <row r="359">
-      <c r="E359" s="21"/>
-      <c r="G359" s="22"/>
+      <c r="E359" s="23"/>
+      <c r="G359" s="24"/>
     </row>
     <row r="360">
-      <c r="E360" s="21"/>
-      <c r="G360" s="22"/>
+      <c r="E360" s="23"/>
+      <c r="G360" s="24"/>
     </row>
     <row r="361">
-      <c r="E361" s="21"/>
-      <c r="G361" s="22"/>
+      <c r="E361" s="23"/>
+      <c r="G361" s="24"/>
     </row>
     <row r="362">
-      <c r="E362" s="21"/>
-      <c r="G362" s="22"/>
+      <c r="E362" s="23"/>
+      <c r="G362" s="24"/>
     </row>
     <row r="363">
-      <c r="E363" s="21"/>
-      <c r="G363" s="22"/>
+      <c r="E363" s="23"/>
+      <c r="G363" s="24"/>
     </row>
     <row r="364">
-      <c r="E364" s="21"/>
-      <c r="G364" s="22"/>
+      <c r="E364" s="23"/>
+      <c r="G364" s="24"/>
     </row>
     <row r="365">
-      <c r="E365" s="21"/>
-      <c r="G365" s="22"/>
+      <c r="E365" s="23"/>
+      <c r="G365" s="24"/>
     </row>
     <row r="366">
-      <c r="E366" s="21"/>
-      <c r="G366" s="22"/>
+      <c r="E366" s="23"/>
+      <c r="G366" s="24"/>
     </row>
     <row r="367">
-      <c r="E367" s="21"/>
-      <c r="G367" s="22"/>
+      <c r="E367" s="23"/>
+      <c r="G367" s="24"/>
     </row>
     <row r="368">
-      <c r="E368" s="21"/>
-      <c r="G368" s="22"/>
+      <c r="E368" s="23"/>
+      <c r="G368" s="24"/>
     </row>
     <row r="369">
-      <c r="E369" s="21"/>
-      <c r="G369" s="22"/>
+      <c r="E369" s="23"/>
+      <c r="G369" s="24"/>
     </row>
     <row r="370">
-      <c r="E370" s="21"/>
-      <c r="G370" s="22"/>
+      <c r="E370" s="23"/>
+      <c r="G370" s="24"/>
     </row>
     <row r="371">
-      <c r="E371" s="21"/>
-      <c r="G371" s="22"/>
+      <c r="E371" s="23"/>
+      <c r="G371" s="24"/>
     </row>
     <row r="372">
-      <c r="E372" s="21"/>
-      <c r="G372" s="22"/>
+      <c r="E372" s="23"/>
+      <c r="G372" s="24"/>
     </row>
     <row r="373">
-      <c r="E373" s="21"/>
-      <c r="G373" s="22"/>
+      <c r="E373" s="23"/>
+      <c r="G373" s="24"/>
     </row>
     <row r="374">
-      <c r="E374" s="21"/>
-      <c r="G374" s="22"/>
+      <c r="E374" s="23"/>
+      <c r="G374" s="24"/>
     </row>
     <row r="375">
-      <c r="E375" s="21"/>
-      <c r="G375" s="22"/>
+      <c r="E375" s="23"/>
+      <c r="G375" s="24"/>
     </row>
     <row r="376">
-      <c r="E376" s="21"/>
-      <c r="G376" s="22"/>
+      <c r="E376" s="23"/>
+      <c r="G376" s="24"/>
     </row>
     <row r="377">
-      <c r="E377" s="21"/>
-      <c r="G377" s="22"/>
+      <c r="E377" s="23"/>
+      <c r="G377" s="24"/>
     </row>
     <row r="378">
-      <c r="E378" s="21"/>
-      <c r="G378" s="22"/>
+      <c r="E378" s="23"/>
+      <c r="G378" s="24"/>
     </row>
     <row r="379">
-      <c r="E379" s="21"/>
-      <c r="G379" s="22"/>
+      <c r="E379" s="23"/>
+      <c r="G379" s="24"/>
     </row>
     <row r="380">
-      <c r="E380" s="21"/>
-      <c r="G380" s="22"/>
+      <c r="E380" s="23"/>
+      <c r="G380" s="24"/>
     </row>
     <row r="381">
-      <c r="E381" s="21"/>
-      <c r="G381" s="22"/>
+      <c r="E381" s="23"/>
+      <c r="G381" s="24"/>
     </row>
     <row r="382">
-      <c r="E382" s="21"/>
-      <c r="G382" s="22"/>
+      <c r="E382" s="23"/>
+      <c r="G382" s="24"/>
     </row>
     <row r="383">
-      <c r="E383" s="21"/>
-      <c r="G383" s="22"/>
+      <c r="E383" s="23"/>
+      <c r="G383" s="24"/>
     </row>
     <row r="384">
-      <c r="E384" s="21"/>
-      <c r="G384" s="22"/>
+      <c r="E384" s="23"/>
+      <c r="G384" s="24"/>
     </row>
     <row r="385">
-      <c r="E385" s="21"/>
-      <c r="G385" s="22"/>
+      <c r="E385" s="23"/>
+      <c r="G385" s="24"/>
     </row>
     <row r="386">
-      <c r="E386" s="21"/>
-      <c r="G386" s="22"/>
+      <c r="E386" s="23"/>
+      <c r="G386" s="24"/>
     </row>
     <row r="387">
-      <c r="E387" s="21"/>
-      <c r="G387" s="22"/>
+      <c r="E387" s="23"/>
+      <c r="G387" s="24"/>
     </row>
     <row r="388">
-      <c r="E388" s="21"/>
-      <c r="G388" s="22"/>
+      <c r="E388" s="23"/>
+      <c r="G388" s="24"/>
     </row>
     <row r="389">
-      <c r="E389" s="21"/>
-      <c r="G389" s="22"/>
+      <c r="E389" s="23"/>
+      <c r="G389" s="24"/>
     </row>
     <row r="390">
-      <c r="E390" s="21"/>
-      <c r="G390" s="22"/>
+      <c r="E390" s="23"/>
+      <c r="G390" s="24"/>
     </row>
     <row r="391">
-      <c r="E391" s="21"/>
-      <c r="G391" s="22"/>
+      <c r="E391" s="23"/>
+      <c r="G391" s="24"/>
     </row>
     <row r="392">
-      <c r="E392" s="21"/>
-      <c r="G392" s="22"/>
+      <c r="E392" s="23"/>
+      <c r="G392" s="24"/>
     </row>
     <row r="393">
-      <c r="E393" s="21"/>
-      <c r="G393" s="22"/>
+      <c r="E393" s="23"/>
+      <c r="G393" s="24"/>
     </row>
     <row r="394">
-      <c r="E394" s="21"/>
-      <c r="G394" s="22"/>
+      <c r="E394" s="23"/>
+      <c r="G394" s="24"/>
     </row>
     <row r="395">
-      <c r="E395" s="21"/>
-      <c r="G395" s="22"/>
+      <c r="E395" s="23"/>
+      <c r="G395" s="24"/>
     </row>
     <row r="396">
-      <c r="E396" s="21"/>
-      <c r="G396" s="22"/>
+      <c r="E396" s="23"/>
+      <c r="G396" s="24"/>
     </row>
     <row r="397">
-      <c r="E397" s="21"/>
-      <c r="G397" s="22"/>
+      <c r="E397" s="23"/>
+      <c r="G397" s="24"/>
     </row>
     <row r="398">
-      <c r="E398" s="21"/>
-      <c r="G398" s="22"/>
+      <c r="E398" s="23"/>
+      <c r="G398" s="24"/>
     </row>
     <row r="399">
-      <c r="E399" s="21"/>
-      <c r="G399" s="22"/>
+      <c r="E399" s="23"/>
+      <c r="G399" s="24"/>
     </row>
     <row r="400">
-      <c r="E400" s="21"/>
-      <c r="G400" s="22"/>
+      <c r="E400" s="23"/>
+      <c r="G400" s="24"/>
     </row>
     <row r="401">
-      <c r="E401" s="21"/>
-      <c r="G401" s="22"/>
+      <c r="E401" s="23"/>
+      <c r="G401" s="24"/>
     </row>
     <row r="402">
-      <c r="E402" s="21"/>
-      <c r="G402" s="22"/>
+      <c r="E402" s="23"/>
+      <c r="G402" s="24"/>
     </row>
     <row r="403">
-      <c r="E403" s="21"/>
-      <c r="G403" s="22"/>
+      <c r="E403" s="23"/>
+      <c r="G403" s="24"/>
     </row>
     <row r="404">
-      <c r="E404" s="21"/>
-      <c r="G404" s="22"/>
+      <c r="E404" s="23"/>
+      <c r="G404" s="24"/>
     </row>
     <row r="405">
-      <c r="E405" s="21"/>
-      <c r="G405" s="22"/>
+      <c r="E405" s="23"/>
+      <c r="G405" s="24"/>
     </row>
     <row r="406">
-      <c r="E406" s="21"/>
-      <c r="G406" s="22"/>
+      <c r="E406" s="23"/>
+      <c r="G406" s="24"/>
     </row>
     <row r="407">
-      <c r="E407" s="21"/>
-      <c r="G407" s="22"/>
+      <c r="E407" s="23"/>
+      <c r="G407" s="24"/>
     </row>
     <row r="408">
-      <c r="E408" s="21"/>
-      <c r="G408" s="22"/>
+      <c r="E408" s="23"/>
+      <c r="G408" s="24"/>
     </row>
     <row r="409">
-      <c r="E409" s="21"/>
-      <c r="G409" s="22"/>
+      <c r="E409" s="23"/>
+      <c r="G409" s="24"/>
     </row>
     <row r="410">
-      <c r="E410" s="21"/>
-      <c r="G410" s="22"/>
+      <c r="E410" s="23"/>
+      <c r="G410" s="24"/>
     </row>
     <row r="411">
-      <c r="E411" s="21"/>
-      <c r="G411" s="22"/>
+      <c r="E411" s="23"/>
+      <c r="G411" s="24"/>
     </row>
     <row r="412">
-      <c r="E412" s="21"/>
-      <c r="G412" s="22"/>
+      <c r="E412" s="23"/>
+      <c r="G412" s="24"/>
     </row>
     <row r="413">
-      <c r="E413" s="21"/>
-      <c r="G413" s="22"/>
+      <c r="E413" s="23"/>
+      <c r="G413" s="24"/>
     </row>
     <row r="414">
-      <c r="E414" s="21"/>
-      <c r="G414" s="22"/>
+      <c r="E414" s="23"/>
+      <c r="G414" s="24"/>
     </row>
     <row r="415">
-      <c r="E415" s="21"/>
-      <c r="G415" s="22"/>
+      <c r="E415" s="23"/>
+      <c r="G415" s="24"/>
     </row>
     <row r="416">
-      <c r="E416" s="21"/>
-      <c r="G416" s="22"/>
+      <c r="E416" s="23"/>
+      <c r="G416" s="24"/>
     </row>
     <row r="417">
-      <c r="E417" s="21"/>
-      <c r="G417" s="22"/>
+      <c r="E417" s="23"/>
+      <c r="G417" s="24"/>
     </row>
     <row r="418">
-      <c r="E418" s="21"/>
-      <c r="G418" s="22"/>
+      <c r="E418" s="23"/>
+      <c r="G418" s="24"/>
     </row>
     <row r="419">
-      <c r="E419" s="21"/>
-      <c r="G419" s="22"/>
+      <c r="E419" s="23"/>
+      <c r="G419" s="24"/>
     </row>
     <row r="420">
-      <c r="E420" s="21"/>
-      <c r="G420" s="22"/>
+      <c r="E420" s="23"/>
+      <c r="G420" s="24"/>
     </row>
     <row r="421">
-      <c r="E421" s="21"/>
-      <c r="G421" s="22"/>
+      <c r="E421" s="23"/>
+      <c r="G421" s="24"/>
     </row>
     <row r="422">
-      <c r="E422" s="21"/>
-      <c r="G422" s="22"/>
+      <c r="E422" s="23"/>
+      <c r="G422" s="24"/>
     </row>
     <row r="423">
-      <c r="E423" s="21"/>
-      <c r="G423" s="22"/>
+      <c r="E423" s="23"/>
+      <c r="G423" s="24"/>
     </row>
     <row r="424">
-      <c r="E424" s="21"/>
-      <c r="G424" s="22"/>
+      <c r="E424" s="23"/>
+      <c r="G424" s="24"/>
     </row>
     <row r="425">
-      <c r="E425" s="21"/>
-      <c r="G425" s="22"/>
+      <c r="E425" s="23"/>
+      <c r="G425" s="24"/>
     </row>
     <row r="426">
-      <c r="E426" s="21"/>
-      <c r="G426" s="22"/>
+      <c r="E426" s="23"/>
+      <c r="G426" s="24"/>
     </row>
     <row r="427">
-      <c r="E427" s="21"/>
-      <c r="G427" s="22"/>
+      <c r="E427" s="23"/>
+      <c r="G427" s="24"/>
     </row>
     <row r="428">
-      <c r="E428" s="21"/>
-      <c r="G428" s="22"/>
+      <c r="E428" s="23"/>
+      <c r="G428" s="24"/>
     </row>
     <row r="429">
-      <c r="E429" s="21"/>
-      <c r="G429" s="22"/>
+      <c r="E429" s="23"/>
+      <c r="G429" s="24"/>
     </row>
     <row r="430">
-      <c r="E430" s="21"/>
-      <c r="G430" s="22"/>
+      <c r="E430" s="23"/>
+      <c r="G430" s="24"/>
     </row>
     <row r="431">
-      <c r="E431" s="21"/>
-      <c r="G431" s="22"/>
+      <c r="E431" s="23"/>
+      <c r="G431" s="24"/>
     </row>
     <row r="432">
-      <c r="E432" s="21"/>
-      <c r="G432" s="22"/>
+      <c r="E432" s="23"/>
+      <c r="G432" s="24"/>
     </row>
     <row r="433">
-      <c r="E433" s="21"/>
-      <c r="G433" s="22"/>
+      <c r="E433" s="23"/>
+      <c r="G433" s="24"/>
     </row>
     <row r="434">
-      <c r="E434" s="21"/>
-      <c r="G434" s="22"/>
+      <c r="E434" s="23"/>
+      <c r="G434" s="24"/>
     </row>
     <row r="435">
-      <c r="E435" s="21"/>
-      <c r="G435" s="22"/>
+      <c r="E435" s="23"/>
+      <c r="G435" s="24"/>
     </row>
     <row r="436">
-      <c r="E436" s="21"/>
-      <c r="G436" s="22"/>
+      <c r="E436" s="23"/>
+      <c r="G436" s="24"/>
     </row>
     <row r="437">
-      <c r="E437" s="21"/>
-      <c r="G437" s="22"/>
+      <c r="E437" s="23"/>
+      <c r="G437" s="24"/>
     </row>
     <row r="438">
-      <c r="E438" s="21"/>
-      <c r="G438" s="22"/>
+      <c r="E438" s="23"/>
+      <c r="G438" s="24"/>
     </row>
     <row r="439">
-      <c r="E439" s="21"/>
-      <c r="G439" s="22"/>
+      <c r="E439" s="23"/>
+      <c r="G439" s="24"/>
     </row>
     <row r="440">
-      <c r="E440" s="21"/>
-      <c r="G440" s="22"/>
+      <c r="E440" s="23"/>
+      <c r="G440" s="24"/>
     </row>
     <row r="441">
-      <c r="E441" s="21"/>
-      <c r="G441" s="22"/>
+      <c r="E441" s="23"/>
+      <c r="G441" s="24"/>
     </row>
     <row r="442">
-      <c r="E442" s="21"/>
-      <c r="G442" s="22"/>
+      <c r="E442" s="23"/>
+      <c r="G442" s="24"/>
     </row>
     <row r="443">
-      <c r="E443" s="21"/>
-      <c r="G443" s="22"/>
+      <c r="E443" s="23"/>
+      <c r="G443" s="24"/>
     </row>
     <row r="444">
-      <c r="E444" s="21"/>
-      <c r="G444" s="22"/>
+      <c r="E444" s="23"/>
+      <c r="G444" s="24"/>
     </row>
     <row r="445">
-      <c r="E445" s="21"/>
-      <c r="G445" s="22"/>
+      <c r="E445" s="23"/>
+      <c r="G445" s="24"/>
     </row>
     <row r="446">
-      <c r="E446" s="21"/>
-      <c r="G446" s="22"/>
+      <c r="E446" s="23"/>
+      <c r="G446" s="24"/>
     </row>
     <row r="447">
-      <c r="E447" s="21"/>
-      <c r="G447" s="22"/>
+      <c r="E447" s="23"/>
+      <c r="G447" s="24"/>
     </row>
     <row r="448">
-      <c r="E448" s="21"/>
-      <c r="G448" s="22"/>
+      <c r="E448" s="23"/>
+      <c r="G448" s="24"/>
     </row>
     <row r="449">
-      <c r="E449" s="21"/>
-      <c r="G449" s="22"/>
+      <c r="E449" s="23"/>
+      <c r="G449" s="24"/>
     </row>
     <row r="450">
-      <c r="E450" s="21"/>
-      <c r="G450" s="22"/>
+      <c r="E450" s="23"/>
+      <c r="G450" s="24"/>
     </row>
     <row r="451">
-      <c r="E451" s="21"/>
-      <c r="G451" s="22"/>
+      <c r="E451" s="23"/>
+      <c r="G451" s="24"/>
     </row>
     <row r="452">
-      <c r="E452" s="21"/>
-      <c r="G452" s="22"/>
+      <c r="E452" s="23"/>
+      <c r="G452" s="24"/>
     </row>
     <row r="453">
-      <c r="E453" s="21"/>
-      <c r="G453" s="22"/>
+      <c r="E453" s="23"/>
+      <c r="G453" s="24"/>
     </row>
     <row r="454">
-      <c r="E454" s="21"/>
-      <c r="G454" s="22"/>
+      <c r="E454" s="23"/>
+      <c r="G454" s="24"/>
     </row>
     <row r="455">
-      <c r="E455" s="21"/>
-      <c r="G455" s="22"/>
+      <c r="E455" s="23"/>
+      <c r="G455" s="24"/>
     </row>
     <row r="456">
-      <c r="E456" s="21"/>
-      <c r="G456" s="22"/>
+      <c r="E456" s="23"/>
+      <c r="G456" s="24"/>
     </row>
     <row r="457">
-      <c r="E457" s="21"/>
-      <c r="G457" s="22"/>
+      <c r="E457" s="23"/>
+      <c r="G457" s="24"/>
     </row>
     <row r="458">
-      <c r="E458" s="21"/>
-      <c r="G458" s="22"/>
+      <c r="E458" s="23"/>
+      <c r="G458" s="24"/>
     </row>
     <row r="459">
-      <c r="E459" s="21"/>
-      <c r="G459" s="22"/>
+      <c r="E459" s="23"/>
+      <c r="G459" s="24"/>
     </row>
     <row r="460">
-      <c r="E460" s="21"/>
-      <c r="G460" s="22"/>
+      <c r="E460" s="23"/>
+      <c r="G460" s="24"/>
     </row>
     <row r="461">
-      <c r="E461" s="21"/>
-      <c r="G461" s="22"/>
+      <c r="E461" s="23"/>
+      <c r="G461" s="24"/>
     </row>
     <row r="462">
-      <c r="E462" s="21"/>
-      <c r="G462" s="22"/>
+      <c r="E462" s="23"/>
+      <c r="G462" s="24"/>
     </row>
     <row r="463">
-      <c r="E463" s="21"/>
-      <c r="G463" s="22"/>
+      <c r="E463" s="23"/>
+      <c r="G463" s="24"/>
     </row>
     <row r="464">
-      <c r="E464" s="21"/>
-      <c r="G464" s="22"/>
+      <c r="E464" s="23"/>
+      <c r="G464" s="24"/>
     </row>
     <row r="465">
-      <c r="E465" s="21"/>
-      <c r="G465" s="22"/>
+      <c r="E465" s="23"/>
+      <c r="G465" s="24"/>
     </row>
     <row r="466">
-      <c r="E466" s="21"/>
-      <c r="G466" s="22"/>
+      <c r="E466" s="23"/>
+      <c r="G466" s="24"/>
     </row>
     <row r="467">
-      <c r="E467" s="21"/>
-      <c r="G467" s="22"/>
+      <c r="E467" s="23"/>
+      <c r="G467" s="24"/>
     </row>
     <row r="468">
-      <c r="E468" s="21"/>
-      <c r="G468" s="22"/>
+      <c r="E468" s="23"/>
+      <c r="G468" s="24"/>
     </row>
     <row r="469">
-      <c r="E469" s="21"/>
-      <c r="G469" s="22"/>
+      <c r="E469" s="23"/>
+      <c r="G469" s="24"/>
     </row>
     <row r="470">
-      <c r="E470" s="21"/>
-      <c r="G470" s="22"/>
+      <c r="E470" s="23"/>
+      <c r="G470" s="24"/>
     </row>
     <row r="471">
-      <c r="E471" s="21"/>
-      <c r="G471" s="22"/>
+      <c r="E471" s="23"/>
+      <c r="G471" s="24"/>
     </row>
     <row r="472">
-      <c r="E472" s="21"/>
-      <c r="G472" s="22"/>
+      <c r="E472" s="23"/>
+      <c r="G472" s="24"/>
     </row>
     <row r="473">
-      <c r="E473" s="21"/>
-      <c r="G473" s="22"/>
+      <c r="E473" s="23"/>
+      <c r="G473" s="24"/>
     </row>
     <row r="474">
-      <c r="E474" s="21"/>
-      <c r="G474" s="22"/>
+      <c r="E474" s="23"/>
+      <c r="G474" s="24"/>
     </row>
     <row r="475">
-      <c r="E475" s="21"/>
-      <c r="G475" s="22"/>
+      <c r="E475" s="23"/>
+      <c r="G475" s="24"/>
     </row>
     <row r="476">
-      <c r="E476" s="21"/>
-      <c r="G476" s="22"/>
+      <c r="E476" s="23"/>
+      <c r="G476" s="24"/>
     </row>
     <row r="477">
-      <c r="E477" s="21"/>
-      <c r="G477" s="22"/>
+      <c r="E477" s="23"/>
+      <c r="G477" s="24"/>
     </row>
     <row r="478">
-      <c r="E478" s="21"/>
-      <c r="G478" s="22"/>
+      <c r="E478" s="23"/>
+      <c r="G478" s="24"/>
     </row>
     <row r="479">
-      <c r="E479" s="21"/>
-      <c r="G479" s="22"/>
+      <c r="E479" s="23"/>
+      <c r="G479" s="24"/>
     </row>
     <row r="480">
-      <c r="E480" s="21"/>
-      <c r="G480" s="22"/>
+      <c r="E480" s="23"/>
+      <c r="G480" s="24"/>
     </row>
     <row r="481">
-      <c r="E481" s="21"/>
-      <c r="G481" s="22"/>
+      <c r="E481" s="23"/>
+      <c r="G481" s="24"/>
     </row>
     <row r="482">
-      <c r="E482" s="21"/>
-      <c r="G482" s="22"/>
+      <c r="E482" s="23"/>
+      <c r="G482" s="24"/>
     </row>
     <row r="483">
-      <c r="E483" s="21"/>
-      <c r="G483" s="22"/>
+      <c r="E483" s="23"/>
+      <c r="G483" s="24"/>
     </row>
     <row r="484">
-      <c r="E484" s="21"/>
-      <c r="G484" s="22"/>
+      <c r="E484" s="23"/>
+      <c r="G484" s="24"/>
     </row>
     <row r="485">
-      <c r="E485" s="21"/>
-      <c r="G485" s="22"/>
+      <c r="E485" s="23"/>
+      <c r="G485" s="24"/>
     </row>
     <row r="486">
-      <c r="E486" s="21"/>
-      <c r="G486" s="22"/>
+      <c r="E486" s="23"/>
+      <c r="G486" s="24"/>
     </row>
     <row r="487">
-      <c r="E487" s="21"/>
-      <c r="G487" s="22"/>
+      <c r="E487" s="23"/>
+      <c r="G487" s="24"/>
     </row>
     <row r="488">
-      <c r="E488" s="21"/>
-      <c r="G488" s="22"/>
+      <c r="E488" s="23"/>
+      <c r="G488" s="24"/>
     </row>
     <row r="489">
-      <c r="E489" s="21"/>
-      <c r="G489" s="22"/>
+      <c r="E489" s="23"/>
+      <c r="G489" s="24"/>
     </row>
     <row r="490">
-      <c r="E490" s="21"/>
-      <c r="G490" s="22"/>
+      <c r="E490" s="23"/>
+      <c r="G490" s="24"/>
     </row>
     <row r="491">
-      <c r="E491" s="21"/>
-      <c r="G491" s="22"/>
+      <c r="E491" s="23"/>
+      <c r="G491" s="24"/>
     </row>
     <row r="492">
-      <c r="E492" s="21"/>
-      <c r="G492" s="22"/>
+      <c r="E492" s="23"/>
+      <c r="G492" s="24"/>
     </row>
     <row r="493">
-      <c r="E493" s="21"/>
-      <c r="G493" s="22"/>
+      <c r="E493" s="23"/>
+      <c r="G493" s="24"/>
     </row>
     <row r="494">
-      <c r="E494" s="21"/>
-      <c r="G494" s="22"/>
+      <c r="E494" s="23"/>
+      <c r="G494" s="24"/>
     </row>
     <row r="495">
-      <c r="E495" s="21"/>
-      <c r="G495" s="22"/>
+      <c r="E495" s="23"/>
+      <c r="G495" s="24"/>
     </row>
     <row r="496">
-      <c r="E496" s="21"/>
-      <c r="G496" s="22"/>
+      <c r="E496" s="23"/>
+      <c r="G496" s="24"/>
     </row>
     <row r="497">
-      <c r="E497" s="21"/>
-      <c r="G497" s="22"/>
+      <c r="E497" s="23"/>
+      <c r="G497" s="24"/>
     </row>
     <row r="498">
-      <c r="E498" s="21"/>
-      <c r="G498" s="22"/>
+      <c r="E498" s="23"/>
+      <c r="G498" s="24"/>
     </row>
     <row r="499">
-      <c r="E499" s="21"/>
-      <c r="G499" s="22"/>
+      <c r="E499" s="23"/>
+      <c r="G499" s="24"/>
     </row>
     <row r="500">
-      <c r="E500" s="21"/>
-      <c r="G500" s="22"/>
+      <c r="E500" s="23"/>
+      <c r="G500" s="24"/>
     </row>
     <row r="501">
-      <c r="E501" s="21"/>
-      <c r="G501" s="22"/>
+      <c r="E501" s="23"/>
+      <c r="G501" s="24"/>
     </row>
     <row r="502">
-      <c r="E502" s="21"/>
-      <c r="G502" s="22"/>
+      <c r="E502" s="23"/>
+      <c r="G502" s="24"/>
     </row>
     <row r="503">
-      <c r="E503" s="21"/>
-      <c r="G503" s="22"/>
+      <c r="E503" s="23"/>
+      <c r="G503" s="24"/>
     </row>
     <row r="504">
-      <c r="E504" s="21"/>
-      <c r="G504" s="22"/>
+      <c r="E504" s="23"/>
+      <c r="G504" s="24"/>
     </row>
     <row r="505">
-      <c r="E505" s="21"/>
-      <c r="G505" s="22"/>
+      <c r="E505" s="23"/>
+      <c r="G505" s="24"/>
     </row>
     <row r="506">
-      <c r="E506" s="21"/>
-      <c r="G506" s="22"/>
+      <c r="E506" s="23"/>
+      <c r="G506" s="24"/>
     </row>
     <row r="507">
-      <c r="E507" s="21"/>
-      <c r="G507" s="22"/>
+      <c r="E507" s="23"/>
+      <c r="G507" s="24"/>
     </row>
     <row r="508">
-      <c r="E508" s="21"/>
-      <c r="G508" s="22"/>
+      <c r="E508" s="23"/>
+      <c r="G508" s="24"/>
     </row>
     <row r="509">
-      <c r="E509" s="21"/>
-      <c r="G509" s="22"/>
+      <c r="E509" s="23"/>
+      <c r="G509" s="24"/>
     </row>
     <row r="510">
-      <c r="E510" s="21"/>
-      <c r="G510" s="22"/>
+      <c r="E510" s="23"/>
+      <c r="G510" s="24"/>
     </row>
     <row r="511">
-      <c r="E511" s="21"/>
-      <c r="G511" s="22"/>
+      <c r="E511" s="23"/>
+      <c r="G511" s="24"/>
     </row>
     <row r="512">
-      <c r="E512" s="21"/>
-      <c r="G512" s="22"/>
+      <c r="E512" s="23"/>
+      <c r="G512" s="24"/>
     </row>
     <row r="513">
-      <c r="E513" s="21"/>
-      <c r="G513" s="22"/>
+      <c r="E513" s="23"/>
+      <c r="G513" s="24"/>
     </row>
     <row r="514">
-      <c r="E514" s="21"/>
-      <c r="G514" s="22"/>
+      <c r="E514" s="23"/>
+      <c r="G514" s="24"/>
     </row>
     <row r="515">
-      <c r="E515" s="21"/>
-      <c r="G515" s="22"/>
+      <c r="E515" s="23"/>
+      <c r="G515" s="24"/>
     </row>
     <row r="516">
-      <c r="E516" s="21"/>
-      <c r="G516" s="22"/>
+      <c r="E516" s="23"/>
+      <c r="G516" s="24"/>
     </row>
     <row r="517">
-      <c r="E517" s="21"/>
-      <c r="G517" s="22"/>
+      <c r="E517" s="23"/>
+      <c r="G517" s="24"/>
     </row>
     <row r="518">
-      <c r="E518" s="21"/>
-      <c r="G518" s="22"/>
+      <c r="E518" s="23"/>
+      <c r="G518" s="24"/>
     </row>
     <row r="519">
-      <c r="E519" s="21"/>
-      <c r="G519" s="22"/>
+      <c r="E519" s="23"/>
+      <c r="G519" s="24"/>
     </row>
     <row r="520">
-      <c r="E520" s="21"/>
-      <c r="G520" s="22"/>
+      <c r="E520" s="23"/>
+      <c r="G520" s="24"/>
     </row>
     <row r="521">
-      <c r="E521" s="21"/>
-      <c r="G521" s="22"/>
+      <c r="E521" s="23"/>
+      <c r="G521" s="24"/>
     </row>
     <row r="522">
-      <c r="E522" s="21"/>
-      <c r="G522" s="22"/>
+      <c r="E522" s="23"/>
+      <c r="G522" s="24"/>
     </row>
     <row r="523">
-      <c r="E523" s="21"/>
-      <c r="G523" s="22"/>
+      <c r="E523" s="23"/>
+      <c r="G523" s="24"/>
     </row>
     <row r="524">
-      <c r="E524" s="21"/>
-      <c r="G524" s="22"/>
+      <c r="E524" s="23"/>
+      <c r="G524" s="24"/>
     </row>
     <row r="525">
-      <c r="E525" s="21"/>
-      <c r="G525" s="22"/>
+      <c r="E525" s="23"/>
+      <c r="G525" s="24"/>
     </row>
     <row r="526">
-      <c r="E526" s="21"/>
-      <c r="G526" s="22"/>
+      <c r="E526" s="23"/>
+      <c r="G526" s="24"/>
     </row>
     <row r="527">
-      <c r="E527" s="21"/>
-      <c r="G527" s="22"/>
+      <c r="E527" s="23"/>
+      <c r="G527" s="24"/>
     </row>
     <row r="528">
-      <c r="E528" s="21"/>
-      <c r="G528" s="22"/>
+      <c r="E528" s="23"/>
+      <c r="G528" s="24"/>
     </row>
     <row r="529">
-      <c r="E529" s="21"/>
-      <c r="G529" s="22"/>
+      <c r="E529" s="23"/>
+      <c r="G529" s="24"/>
     </row>
     <row r="530">
-      <c r="E530" s="21"/>
-      <c r="G530" s="22"/>
+      <c r="E530" s="23"/>
+      <c r="G530" s="24"/>
     </row>
     <row r="531">
-      <c r="E531" s="21"/>
-      <c r="G531" s="22"/>
+      <c r="E531" s="23"/>
+      <c r="G531" s="24"/>
     </row>
     <row r="532">
-      <c r="E532" s="21"/>
-      <c r="G532" s="22"/>
+      <c r="E532" s="23"/>
+      <c r="G532" s="24"/>
     </row>
     <row r="533">
-      <c r="E533" s="21"/>
-      <c r="G533" s="22"/>
+      <c r="E533" s="23"/>
+      <c r="G533" s="24"/>
     </row>
     <row r="534">
-      <c r="E534" s="21"/>
-      <c r="G534" s="22"/>
+      <c r="E534" s="23"/>
+      <c r="G534" s="24"/>
     </row>
     <row r="535">
-      <c r="E535" s="21"/>
-      <c r="G535" s="22"/>
+      <c r="E535" s="23"/>
+      <c r="G535" s="24"/>
     </row>
     <row r="536">
-      <c r="E536" s="21"/>
-      <c r="G536" s="22"/>
+      <c r="E536" s="23"/>
+      <c r="G536" s="24"/>
     </row>
     <row r="537">
-      <c r="E537" s="21"/>
-      <c r="G537" s="22"/>
+      <c r="E537" s="23"/>
+      <c r="G537" s="24"/>
     </row>
     <row r="538">
-      <c r="E538" s="21"/>
-      <c r="G538" s="22"/>
+      <c r="E538" s="23"/>
+      <c r="G538" s="24"/>
     </row>
     <row r="539">
-      <c r="E539" s="21"/>
-      <c r="G539" s="22"/>
+      <c r="E539" s="23"/>
+      <c r="G539" s="24"/>
     </row>
     <row r="540">
-      <c r="E540" s="21"/>
-      <c r="G540" s="22"/>
+      <c r="E540" s="23"/>
+      <c r="G540" s="24"/>
     </row>
     <row r="541">
-      <c r="E541" s="21"/>
-      <c r="G541" s="22"/>
+      <c r="E541" s="23"/>
+      <c r="G541" s="24"/>
     </row>
     <row r="542">
-      <c r="E542" s="21"/>
-      <c r="G542" s="22"/>
+      <c r="E542" s="23"/>
+      <c r="G542" s="24"/>
     </row>
     <row r="543">
-      <c r="E543" s="21"/>
-      <c r="G543" s="22"/>
+      <c r="E543" s="23"/>
+      <c r="G543" s="24"/>
     </row>
     <row r="544">
-      <c r="E544" s="21"/>
-      <c r="G544" s="22"/>
+      <c r="E544" s="23"/>
+      <c r="G544" s="24"/>
     </row>
     <row r="545">
-      <c r="E545" s="21"/>
-      <c r="G545" s="22"/>
+      <c r="E545" s="23"/>
+      <c r="G545" s="24"/>
     </row>
     <row r="546">
-      <c r="E546" s="21"/>
-      <c r="G546" s="22"/>
+      <c r="E546" s="23"/>
+      <c r="G546" s="24"/>
     </row>
     <row r="547">
-      <c r="E547" s="21"/>
-      <c r="G547" s="22"/>
+      <c r="E547" s="23"/>
+      <c r="G547" s="24"/>
     </row>
     <row r="548">
-      <c r="E548" s="21"/>
-      <c r="G548" s="22"/>
+      <c r="E548" s="23"/>
+      <c r="G548" s="24"/>
     </row>
     <row r="549">
-      <c r="E549" s="21"/>
-      <c r="G549" s="22"/>
+      <c r="E549" s="23"/>
+      <c r="G549" s="24"/>
     </row>
     <row r="550">
-      <c r="E550" s="21"/>
-      <c r="G550" s="22"/>
+      <c r="E550" s="23"/>
+      <c r="G550" s="24"/>
     </row>
     <row r="551">
-      <c r="E551" s="21"/>
-      <c r="G551" s="22"/>
+      <c r="E551" s="23"/>
+      <c r="G551" s="24"/>
     </row>
     <row r="552">
-      <c r="E552" s="21"/>
-      <c r="G552" s="22"/>
+      <c r="E552" s="23"/>
+      <c r="G552" s="24"/>
     </row>
     <row r="553">
-      <c r="E553" s="21"/>
-      <c r="G553" s="22"/>
+      <c r="E553" s="23"/>
+      <c r="G553" s="24"/>
     </row>
     <row r="554">
-      <c r="E554" s="21"/>
-      <c r="G554" s="22"/>
+      <c r="E554" s="23"/>
+      <c r="G554" s="24"/>
     </row>
     <row r="555">
-      <c r="E555" s="21"/>
-      <c r="G555" s="22"/>
+      <c r="E555" s="23"/>
+      <c r="G555" s="24"/>
     </row>
     <row r="556">
-      <c r="E556" s="21"/>
-      <c r="G556" s="22"/>
+      <c r="E556" s="23"/>
+      <c r="G556" s="24"/>
     </row>
     <row r="557">
-      <c r="E557" s="21"/>
-      <c r="G557" s="22"/>
+      <c r="E557" s="23"/>
+      <c r="G557" s="24"/>
     </row>
     <row r="558">
-      <c r="E558" s="21"/>
-      <c r="G558" s="22"/>
+      <c r="E558" s="23"/>
+      <c r="G558" s="24"/>
     </row>
     <row r="559">
-      <c r="E559" s="21"/>
-      <c r="G559" s="22"/>
+      <c r="E559" s="23"/>
+      <c r="G559" s="24"/>
     </row>
     <row r="560">
-      <c r="E560" s="21"/>
-      <c r="G560" s="22"/>
+      <c r="E560" s="23"/>
+      <c r="G560" s="24"/>
     </row>
     <row r="561">
-      <c r="E561" s="21"/>
-      <c r="G561" s="22"/>
+      <c r="E561" s="23"/>
+      <c r="G561" s="24"/>
     </row>
     <row r="562">
-      <c r="E562" s="21"/>
-      <c r="G562" s="22"/>
+      <c r="E562" s="23"/>
+      <c r="G562" s="24"/>
     </row>
     <row r="563">
-      <c r="E563" s="21"/>
-      <c r="G563" s="22"/>
+      <c r="E563" s="23"/>
+      <c r="G563" s="24"/>
     </row>
     <row r="564">
-      <c r="E564" s="21"/>
-      <c r="G564" s="22"/>
+      <c r="E564" s="23"/>
+      <c r="G564" s="24"/>
     </row>
     <row r="565">
-      <c r="E565" s="21"/>
-      <c r="G565" s="22"/>
+      <c r="E565" s="23"/>
+      <c r="G565" s="24"/>
     </row>
     <row r="566">
-      <c r="E566" s="21"/>
-      <c r="G566" s="22"/>
+      <c r="E566" s="23"/>
+      <c r="G566" s="24"/>
     </row>
     <row r="567">
-      <c r="E567" s="21"/>
-      <c r="G567" s="22"/>
+      <c r="E567" s="23"/>
+      <c r="G567" s="24"/>
     </row>
     <row r="568">
-      <c r="E568" s="21"/>
-      <c r="G568" s="22"/>
+      <c r="E568" s="23"/>
+      <c r="G568" s="24"/>
     </row>
     <row r="569">
-      <c r="E569" s="21"/>
-      <c r="G569" s="22"/>
+      <c r="E569" s="23"/>
+      <c r="G569" s="24"/>
     </row>
     <row r="570">
-      <c r="E570" s="21"/>
-      <c r="G570" s="22"/>
+      <c r="E570" s="23"/>
+      <c r="G570" s="24"/>
     </row>
     <row r="571">
-      <c r="E571" s="21"/>
-      <c r="G571" s="22"/>
+      <c r="E571" s="23"/>
+      <c r="G571" s="24"/>
     </row>
     <row r="572">
-      <c r="E572" s="21"/>
-      <c r="G572" s="22"/>
+      <c r="E572" s="23"/>
+      <c r="G572" s="24"/>
     </row>
     <row r="573">
-      <c r="E573" s="21"/>
-      <c r="G573" s="22"/>
+      <c r="E573" s="23"/>
+      <c r="G573" s="24"/>
     </row>
     <row r="574">
-      <c r="E574" s="21"/>
-      <c r="G574" s="22"/>
+      <c r="E574" s="23"/>
+      <c r="G574" s="24"/>
     </row>
     <row r="575">
-      <c r="E575" s="21"/>
-      <c r="G575" s="22"/>
+      <c r="E575" s="23"/>
+      <c r="G575" s="24"/>
     </row>
     <row r="576">
-      <c r="E576" s="21"/>
-      <c r="G576" s="22"/>
+      <c r="E576" s="23"/>
+      <c r="G576" s="24"/>
     </row>
     <row r="577">
-      <c r="E577" s="21"/>
-      <c r="G577" s="22"/>
+      <c r="E577" s="23"/>
+      <c r="G577" s="24"/>
     </row>
     <row r="578">
-      <c r="E578" s="21"/>
-      <c r="G578" s="22"/>
+      <c r="E578" s="23"/>
+      <c r="G578" s="24"/>
     </row>
     <row r="579">
-      <c r="E579" s="21"/>
-      <c r="G579" s="22"/>
+      <c r="E579" s="23"/>
+      <c r="G579" s="24"/>
     </row>
     <row r="580">
-      <c r="E580" s="21"/>
-      <c r="G580" s="22"/>
+      <c r="E580" s="23"/>
+      <c r="G580" s="24"/>
     </row>
     <row r="581">
-      <c r="E581" s="21"/>
-      <c r="G581" s="22"/>
+      <c r="E581" s="23"/>
+      <c r="G581" s="24"/>
     </row>
     <row r="582">
-      <c r="E582" s="21"/>
-      <c r="G582" s="22"/>
+      <c r="E582" s="23"/>
+      <c r="G582" s="24"/>
     </row>
     <row r="583">
-      <c r="E583" s="21"/>
-      <c r="G583" s="22"/>
+      <c r="E583" s="23"/>
+      <c r="G583" s="24"/>
     </row>
     <row r="584">
-      <c r="E584" s="21"/>
-      <c r="G584" s="22"/>
+      <c r="E584" s="23"/>
+      <c r="G584" s="24"/>
     </row>
     <row r="585">
-      <c r="E585" s="21"/>
-      <c r="G585" s="22"/>
+      <c r="E585" s="23"/>
+      <c r="G585" s="24"/>
     </row>
     <row r="586">
-      <c r="E586" s="21"/>
-      <c r="G586" s="22"/>
+      <c r="E586" s="23"/>
+      <c r="G586" s="24"/>
     </row>
     <row r="587">
-      <c r="E587" s="21"/>
-      <c r="G587" s="22"/>
+      <c r="E587" s="23"/>
+      <c r="G587" s="24"/>
     </row>
     <row r="588">
-      <c r="E588" s="21"/>
-      <c r="G588" s="22"/>
+      <c r="E588" s="23"/>
+      <c r="G588" s="24"/>
     </row>
     <row r="589">
-      <c r="E589" s="21"/>
-      <c r="G589" s="22"/>
+      <c r="E589" s="23"/>
+      <c r="G589" s="24"/>
     </row>
     <row r="590">
-      <c r="E590" s="21"/>
-      <c r="G590" s="22"/>
+      <c r="E590" s="23"/>
+      <c r="G590" s="24"/>
     </row>
     <row r="591">
-      <c r="E591" s="21"/>
-      <c r="G591" s="22"/>
+      <c r="E591" s="23"/>
+      <c r="G591" s="24"/>
     </row>
     <row r="592">
-      <c r="E592" s="21"/>
-      <c r="G592" s="22"/>
+      <c r="E592" s="23"/>
+      <c r="G592" s="24"/>
     </row>
     <row r="593">
-      <c r="E593" s="21"/>
-      <c r="G593" s="22"/>
+      <c r="E593" s="23"/>
+      <c r="G593" s="24"/>
     </row>
     <row r="594">
-      <c r="E594" s="21"/>
-      <c r="G594" s="22"/>
+      <c r="E594" s="23"/>
+      <c r="G594" s="24"/>
     </row>
     <row r="595">
-      <c r="E595" s="21"/>
-      <c r="G595" s="22"/>
+      <c r="E595" s="23"/>
+      <c r="G595" s="24"/>
     </row>
     <row r="596">
-      <c r="E596" s="21"/>
-      <c r="G596" s="22"/>
+      <c r="E596" s="23"/>
+      <c r="G596" s="24"/>
     </row>
     <row r="597">
-      <c r="E597" s="21"/>
-      <c r="G597" s="22"/>
+      <c r="E597" s="23"/>
+      <c r="G597" s="24"/>
     </row>
     <row r="598">
-      <c r="E598" s="21"/>
-      <c r="G598" s="22"/>
+      <c r="E598" s="23"/>
+      <c r="G598" s="24"/>
     </row>
     <row r="599">
-      <c r="E599" s="21"/>
-      <c r="G599" s="22"/>
+      <c r="E599" s="23"/>
+      <c r="G599" s="24"/>
     </row>
     <row r="600">
-      <c r="E600" s="21"/>
-      <c r="G600" s="22"/>
+      <c r="E600" s="23"/>
+      <c r="G600" s="24"/>
     </row>
     <row r="601">
-      <c r="E601" s="21"/>
-      <c r="G601" s="22"/>
+      <c r="E601" s="23"/>
+      <c r="G601" s="24"/>
     </row>
     <row r="602">
-      <c r="E602" s="21"/>
-      <c r="G602" s="22"/>
+      <c r="E602" s="23"/>
+      <c r="G602" s="24"/>
     </row>
     <row r="603">
-      <c r="E603" s="21"/>
-      <c r="G603" s="22"/>
+      <c r="E603" s="23"/>
+      <c r="G603" s="24"/>
     </row>
     <row r="604">
-      <c r="E604" s="21"/>
-      <c r="G604" s="22"/>
+      <c r="E604" s="23"/>
+      <c r="G604" s="24"/>
     </row>
     <row r="605">
-      <c r="E605" s="21"/>
-      <c r="G605" s="22"/>
+      <c r="E605" s="23"/>
+      <c r="G605" s="24"/>
     </row>
     <row r="606">
-      <c r="E606" s="21"/>
-      <c r="G606" s="22"/>
+      <c r="E606" s="23"/>
+      <c r="G606" s="24"/>
     </row>
     <row r="607">
-      <c r="E607" s="21"/>
-      <c r="G607" s="22"/>
+      <c r="E607" s="23"/>
+      <c r="G607" s="24"/>
     </row>
     <row r="608">
-      <c r="E608" s="21"/>
-      <c r="G608" s="22"/>
+      <c r="E608" s="23"/>
+      <c r="G608" s="24"/>
     </row>
     <row r="609">
-      <c r="E609" s="21"/>
-      <c r="G609" s="22"/>
+      <c r="E609" s="23"/>
+      <c r="G609" s="24"/>
     </row>
     <row r="610">
-      <c r="E610" s="21"/>
-      <c r="G610" s="22"/>
+      <c r="E610" s="23"/>
+      <c r="G610" s="24"/>
     </row>
     <row r="611">
-      <c r="E611" s="21"/>
-      <c r="G611" s="22"/>
+      <c r="E611" s="23"/>
+      <c r="G611" s="24"/>
     </row>
     <row r="612">
-      <c r="E612" s="21"/>
-      <c r="G612" s="22"/>
+      <c r="E612" s="23"/>
+      <c r="G612" s="24"/>
     </row>
     <row r="613">
-      <c r="E613" s="21"/>
-      <c r="G613" s="22"/>
+      <c r="E613" s="23"/>
+      <c r="G613" s="24"/>
     </row>
     <row r="614">
-      <c r="E614" s="21"/>
-      <c r="G614" s="22"/>
+      <c r="E614" s="23"/>
+      <c r="G614" s="24"/>
     </row>
     <row r="615">
-      <c r="E615" s="21"/>
-      <c r="G615" s="22"/>
+      <c r="E615" s="23"/>
+      <c r="G615" s="24"/>
     </row>
     <row r="616">
-      <c r="E616" s="21"/>
-      <c r="G616" s="22"/>
+      <c r="E616" s="23"/>
+      <c r="G616" s="24"/>
     </row>
     <row r="617">
-      <c r="E617" s="21"/>
-      <c r="G617" s="22"/>
+      <c r="E617" s="23"/>
+      <c r="G617" s="24"/>
     </row>
     <row r="618">
-      <c r="E618" s="21"/>
-      <c r="G618" s="22"/>
+      <c r="E618" s="23"/>
+      <c r="G618" s="24"/>
     </row>
     <row r="619">
-      <c r="E619" s="21"/>
-      <c r="G619" s="22"/>
+      <c r="E619" s="23"/>
+      <c r="G619" s="24"/>
     </row>
     <row r="620">
-      <c r="E620" s="21"/>
-      <c r="G620" s="22"/>
+      <c r="E620" s="23"/>
+      <c r="G620" s="24"/>
     </row>
     <row r="621">
-      <c r="E621" s="21"/>
-      <c r="G621" s="22"/>
+      <c r="E621" s="23"/>
+      <c r="G621" s="24"/>
     </row>
     <row r="622">
-      <c r="E622" s="21"/>
-      <c r="G622" s="22"/>
+      <c r="E622" s="23"/>
+      <c r="G622" s="24"/>
     </row>
     <row r="623">
-      <c r="E623" s="21"/>
-      <c r="G623" s="22"/>
+      <c r="E623" s="23"/>
+      <c r="G623" s="24"/>
     </row>
     <row r="624">
-      <c r="E624" s="21"/>
-      <c r="G624" s="22"/>
+      <c r="E624" s="23"/>
+      <c r="G624" s="24"/>
     </row>
     <row r="625">
-      <c r="E625" s="21"/>
-      <c r="G625" s="22"/>
+      <c r="E625" s="23"/>
+      <c r="G625" s="24"/>
     </row>
     <row r="626">
-      <c r="E626" s="21"/>
-      <c r="G626" s="22"/>
+      <c r="E626" s="23"/>
+      <c r="G626" s="24"/>
     </row>
     <row r="627">
-      <c r="E627" s="21"/>
-      <c r="G627" s="22"/>
+      <c r="E627" s="23"/>
+      <c r="G627" s="24"/>
     </row>
     <row r="628">
-      <c r="E628" s="21"/>
-      <c r="G628" s="22"/>
+      <c r="E628" s="23"/>
+      <c r="G628" s="24"/>
     </row>
     <row r="629">
-      <c r="E629" s="21"/>
-      <c r="G629" s="22"/>
+      <c r="E629" s="23"/>
+      <c r="G629" s="24"/>
     </row>
     <row r="630">
-      <c r="E630" s="21"/>
-      <c r="G630" s="22"/>
+      <c r="E630" s="23"/>
+      <c r="G630" s="24"/>
     </row>
     <row r="631">
-      <c r="E631" s="21"/>
-      <c r="G631" s="22"/>
+      <c r="E631" s="23"/>
+      <c r="G631" s="24"/>
     </row>
     <row r="632">
-      <c r="E632" s="21"/>
-      <c r="G632" s="22"/>
+      <c r="E632" s="23"/>
+      <c r="G632" s="24"/>
     </row>
     <row r="633">
-      <c r="E633" s="21"/>
-      <c r="G633" s="22"/>
+      <c r="E633" s="23"/>
+      <c r="G633" s="24"/>
     </row>
     <row r="634">
-      <c r="E634" s="21"/>
-      <c r="G634" s="22"/>
+      <c r="E634" s="23"/>
+      <c r="G634" s="24"/>
     </row>
     <row r="635">
-      <c r="E635" s="21"/>
-      <c r="G635" s="22"/>
+      <c r="E635" s="23"/>
+      <c r="G635" s="24"/>
     </row>
     <row r="636">
-      <c r="E636" s="21"/>
-      <c r="G636" s="22"/>
+      <c r="E636" s="23"/>
+      <c r="G636" s="24"/>
     </row>
     <row r="637">
-      <c r="E637" s="21"/>
-      <c r="G637" s="22"/>
+      <c r="E637" s="23"/>
+      <c r="G637" s="24"/>
     </row>
     <row r="638">
-      <c r="E638" s="21"/>
-      <c r="G638" s="22"/>
+      <c r="E638" s="23"/>
+      <c r="G638" s="24"/>
     </row>
     <row r="639">
-      <c r="E639" s="21"/>
-      <c r="G639" s="22"/>
+      <c r="E639" s="23"/>
+      <c r="G639" s="24"/>
     </row>
     <row r="640">
-      <c r="E640" s="21"/>
-      <c r="G640" s="22"/>
+      <c r="E640" s="23"/>
+      <c r="G640" s="24"/>
     </row>
     <row r="641">
-      <c r="E641" s="21"/>
-      <c r="G641" s="22"/>
+      <c r="E641" s="23"/>
+      <c r="G641" s="24"/>
     </row>
     <row r="642">
-      <c r="E642" s="21"/>
-      <c r="G642" s="22"/>
+      <c r="E642" s="23"/>
+      <c r="G642" s="24"/>
     </row>
     <row r="643">
-      <c r="E643" s="21"/>
-      <c r="G643" s="22"/>
+      <c r="E643" s="23"/>
+      <c r="G643" s="24"/>
     </row>
     <row r="644">
-      <c r="E644" s="21"/>
-      <c r="G644" s="22"/>
+      <c r="E644" s="23"/>
+      <c r="G644" s="24"/>
     </row>
     <row r="645">
-      <c r="E645" s="21"/>
-      <c r="G645" s="22"/>
+      <c r="E645" s="23"/>
+      <c r="G645" s="24"/>
     </row>
     <row r="646">
-      <c r="E646" s="21"/>
-      <c r="G646" s="22"/>
+      <c r="E646" s="23"/>
+      <c r="G646" s="24"/>
     </row>
     <row r="647">
-      <c r="E647" s="21"/>
-      <c r="G647" s="22"/>
+      <c r="E647" s="23"/>
+      <c r="G647" s="24"/>
     </row>
     <row r="648">
-      <c r="E648" s="21"/>
-      <c r="G648" s="22"/>
+      <c r="E648" s="23"/>
+      <c r="G648" s="24"/>
     </row>
     <row r="649">
-      <c r="E649" s="21"/>
-      <c r="G649" s="22"/>
+      <c r="E649" s="23"/>
+      <c r="G649" s="24"/>
     </row>
     <row r="650">
-      <c r="E650" s="21"/>
-      <c r="G650" s="22"/>
+      <c r="E650" s="23"/>
+      <c r="G650" s="24"/>
     </row>
     <row r="651">
-      <c r="E651" s="21"/>
-      <c r="G651" s="22"/>
+      <c r="E651" s="23"/>
+      <c r="G651" s="24"/>
     </row>
     <row r="652">
-      <c r="E652" s="21"/>
-      <c r="G652" s="22"/>
+      <c r="E652" s="23"/>
+      <c r="G652" s="24"/>
     </row>
     <row r="653">
-      <c r="E653" s="21"/>
-      <c r="G653" s="22"/>
+      <c r="E653" s="23"/>
+      <c r="G653" s="24"/>
     </row>
     <row r="654">
-      <c r="E654" s="21"/>
-      <c r="G654" s="22"/>
+      <c r="E654" s="23"/>
+      <c r="G654" s="24"/>
     </row>
     <row r="655">
-      <c r="E655" s="21"/>
-      <c r="G655" s="22"/>
+      <c r="E655" s="23"/>
+      <c r="G655" s="24"/>
     </row>
     <row r="656">
-      <c r="E656" s="21"/>
-      <c r="G656" s="22"/>
+      <c r="E656" s="23"/>
+      <c r="G656" s="24"/>
     </row>
     <row r="657">
-      <c r="E657" s="21"/>
-      <c r="G657" s="22"/>
+      <c r="E657" s="23"/>
+      <c r="G657" s="24"/>
     </row>
     <row r="658">
-      <c r="E658" s="21"/>
-      <c r="G658" s="22"/>
+      <c r="E658" s="23"/>
+      <c r="G658" s="24"/>
     </row>
     <row r="659">
-      <c r="E659" s="21"/>
-      <c r="G659" s="22"/>
+      <c r="E659" s="23"/>
+      <c r="G659" s="24"/>
     </row>
     <row r="660">
-      <c r="E660" s="21"/>
-      <c r="G660" s="22"/>
+      <c r="E660" s="23"/>
+      <c r="G660" s="24"/>
     </row>
     <row r="661">
-      <c r="E661" s="21"/>
-      <c r="G661" s="22"/>
+      <c r="E661" s="23"/>
+      <c r="G661" s="24"/>
     </row>
     <row r="662">
-      <c r="E662" s="21"/>
-      <c r="G662" s="22"/>
+      <c r="E662" s="23"/>
+      <c r="G662" s="24"/>
     </row>
     <row r="663">
-      <c r="E663" s="21"/>
-      <c r="G663" s="22"/>
+      <c r="E663" s="23"/>
+      <c r="G663" s="24"/>
     </row>
     <row r="664">
-      <c r="E664" s="21"/>
-      <c r="G664" s="22"/>
+      <c r="E664" s="23"/>
+      <c r="G664" s="24"/>
     </row>
     <row r="665">
-      <c r="E665" s="21"/>
-      <c r="G665" s="22"/>
+      <c r="E665" s="23"/>
+      <c r="G665" s="24"/>
     </row>
     <row r="666">
-      <c r="E666" s="21"/>
-      <c r="G666" s="22"/>
+      <c r="E666" s="23"/>
+      <c r="G666" s="24"/>
     </row>
     <row r="667">
-      <c r="E667" s="21"/>
-      <c r="G667" s="22"/>
+      <c r="E667" s="23"/>
+      <c r="G667" s="24"/>
     </row>
     <row r="668">
-      <c r="E668" s="21"/>
-      <c r="G668" s="22"/>
+      <c r="E668" s="23"/>
+      <c r="G668" s="24"/>
     </row>
     <row r="669">
-      <c r="E669" s="21"/>
-      <c r="G669" s="22"/>
+      <c r="E669" s="23"/>
+      <c r="G669" s="24"/>
     </row>
     <row r="670">
-      <c r="E670" s="21"/>
-      <c r="G670" s="22"/>
+      <c r="E670" s="23"/>
+      <c r="G670" s="24"/>
     </row>
     <row r="671">
-      <c r="E671" s="21"/>
-      <c r="G671" s="22"/>
+      <c r="E671" s="23"/>
+      <c r="G671" s="24"/>
     </row>
     <row r="672">
-      <c r="E672" s="21"/>
-      <c r="G672" s="22"/>
+      <c r="E672" s="23"/>
+      <c r="G672" s="24"/>
     </row>
     <row r="673">
-      <c r="E673" s="21"/>
-      <c r="G673" s="22"/>
+      <c r="E673" s="23"/>
+      <c r="G673" s="24"/>
     </row>
     <row r="674">
-      <c r="E674" s="21"/>
-      <c r="G674" s="22"/>
+      <c r="E674" s="23"/>
+      <c r="G674" s="24"/>
     </row>
     <row r="675">
-      <c r="E675" s="21"/>
-      <c r="G675" s="22"/>
+      <c r="E675" s="23"/>
+      <c r="G675" s="24"/>
     </row>
     <row r="676">
-      <c r="E676" s="21"/>
-      <c r="G676" s="22"/>
+      <c r="E676" s="23"/>
+      <c r="G676" s="24"/>
     </row>
     <row r="677">
-      <c r="E677" s="21"/>
-      <c r="G677" s="22"/>
+      <c r="E677" s="23"/>
+      <c r="G677" s="24"/>
     </row>
     <row r="678">
-      <c r="E678" s="21"/>
-      <c r="G678" s="22"/>
+      <c r="E678" s="23"/>
+      <c r="G678" s="24"/>
     </row>
     <row r="679">
-      <c r="E679" s="21"/>
-      <c r="G679" s="22"/>
+      <c r="E679" s="23"/>
+      <c r="G679" s="24"/>
     </row>
     <row r="680">
-      <c r="E680" s="21"/>
-      <c r="G680" s="22"/>
+      <c r="E680" s="23"/>
+      <c r="G680" s="24"/>
     </row>
     <row r="681">
-      <c r="E681" s="21"/>
-      <c r="G681" s="22"/>
+      <c r="E681" s="23"/>
+      <c r="G681" s="24"/>
     </row>
     <row r="682">
-      <c r="E682" s="21"/>
-      <c r="G682" s="22"/>
+      <c r="E682" s="23"/>
+      <c r="G682" s="24"/>
     </row>
     <row r="683">
-      <c r="E683" s="21"/>
-      <c r="G683" s="22"/>
+      <c r="E683" s="23"/>
+      <c r="G683" s="24"/>
     </row>
     <row r="684">
-      <c r="E684" s="21"/>
-      <c r="G684" s="22"/>
+      <c r="E684" s="23"/>
+      <c r="G684" s="24"/>
     </row>
     <row r="685">
-      <c r="E685" s="21"/>
-      <c r="G685" s="22"/>
+      <c r="E685" s="23"/>
+      <c r="G685" s="24"/>
     </row>
     <row r="686">
-      <c r="E686" s="21"/>
-      <c r="G686" s="22"/>
+      <c r="E686" s="23"/>
+      <c r="G686" s="24"/>
     </row>
     <row r="687">
-      <c r="E687" s="21"/>
-      <c r="G687" s="22"/>
+      <c r="E687" s="23"/>
+      <c r="G687" s="24"/>
     </row>
     <row r="688">
-      <c r="E688" s="21"/>
-      <c r="G688" s="22"/>
+      <c r="E688" s="23"/>
+      <c r="G688" s="24"/>
     </row>
     <row r="689">
-      <c r="E689" s="21"/>
-      <c r="G689" s="22"/>
+      <c r="E689" s="23"/>
+      <c r="G689" s="24"/>
     </row>
     <row r="690">
-      <c r="E690" s="21"/>
-      <c r="G690" s="22"/>
+      <c r="E690" s="23"/>
+      <c r="G690" s="24"/>
     </row>
     <row r="691">
-      <c r="E691" s="21"/>
-      <c r="G691" s="22"/>
+      <c r="E691" s="23"/>
+      <c r="G691" s="24"/>
     </row>
     <row r="692">
-      <c r="E692" s="21"/>
-      <c r="G692" s="22"/>
+      <c r="E692" s="23"/>
+      <c r="G692" s="24"/>
     </row>
     <row r="693">
-      <c r="E693" s="21"/>
-      <c r="G693" s="22"/>
+      <c r="E693" s="23"/>
+      <c r="G693" s="24"/>
     </row>
     <row r="694">
-      <c r="E694" s="21"/>
-      <c r="G694" s="22"/>
+      <c r="E694" s="23"/>
+      <c r="G694" s="24"/>
     </row>
     <row r="695">
-      <c r="E695" s="21"/>
-      <c r="G695" s="22"/>
+      <c r="E695" s="23"/>
+      <c r="G695" s="24"/>
     </row>
     <row r="696">
-      <c r="E696" s="21"/>
-      <c r="G696" s="22"/>
+      <c r="E696" s="23"/>
+      <c r="G696" s="24"/>
     </row>
     <row r="697">
-      <c r="E697" s="21"/>
-      <c r="G697" s="22"/>
+      <c r="E697" s="23"/>
+      <c r="G697" s="24"/>
     </row>
     <row r="698">
-      <c r="E698" s="21"/>
-      <c r="G698" s="22"/>
+      <c r="E698" s="23"/>
+      <c r="G698" s="24"/>
     </row>
     <row r="699">
-      <c r="E699" s="21"/>
-      <c r="G699" s="22"/>
+      <c r="E699" s="23"/>
+      <c r="G699" s="24"/>
     </row>
     <row r="700">
-      <c r="E700" s="21"/>
-      <c r="G700" s="22"/>
+      <c r="E700" s="23"/>
+      <c r="G700" s="24"/>
     </row>
     <row r="701">
-      <c r="E701" s="21"/>
-      <c r="G701" s="22"/>
+      <c r="E701" s="23"/>
+      <c r="G701" s="24"/>
     </row>
     <row r="702">
-      <c r="E702" s="21"/>
-      <c r="G702" s="22"/>
+      <c r="E702" s="23"/>
+      <c r="G702" s="24"/>
     </row>
     <row r="703">
-      <c r="E703" s="21"/>
-      <c r="G703" s="22"/>
+      <c r="E703" s="23"/>
+      <c r="G703" s="24"/>
     </row>
     <row r="704">
-      <c r="E704" s="21"/>
-      <c r="G704" s="22"/>
+      <c r="E704" s="23"/>
+      <c r="G704" s="24"/>
     </row>
     <row r="705">
-      <c r="E705" s="21"/>
-      <c r="G705" s="22"/>
+      <c r="E705" s="23"/>
+      <c r="G705" s="24"/>
     </row>
     <row r="706">
-      <c r="E706" s="21"/>
-      <c r="G706" s="22"/>
+      <c r="E706" s="23"/>
+      <c r="G706" s="24"/>
     </row>
     <row r="707">
-      <c r="E707" s="21"/>
-      <c r="G707" s="22"/>
+      <c r="E707" s="23"/>
+      <c r="G707" s="24"/>
     </row>
     <row r="708">
-      <c r="E708" s="21"/>
-      <c r="G708" s="22"/>
+      <c r="E708" s="23"/>
+      <c r="G708" s="24"/>
     </row>
     <row r="709">
-      <c r="E709" s="21"/>
-      <c r="G709" s="22"/>
+      <c r="E709" s="23"/>
+      <c r="G709" s="24"/>
     </row>
     <row r="710">
-      <c r="E710" s="21"/>
-      <c r="G710" s="22"/>
+      <c r="E710" s="23"/>
+      <c r="G710" s="24"/>
     </row>
     <row r="711">
-      <c r="E711" s="21"/>
-      <c r="G711" s="22"/>
+      <c r="E711" s="23"/>
+      <c r="G711" s="24"/>
     </row>
     <row r="712">
-      <c r="E712" s="21"/>
-      <c r="G712" s="22"/>
+      <c r="E712" s="23"/>
+      <c r="G712" s="24"/>
     </row>
     <row r="713">
-      <c r="E713" s="21"/>
-      <c r="G713" s="22"/>
+      <c r="E713" s="23"/>
+      <c r="G713" s="24"/>
     </row>
     <row r="714">
-      <c r="E714" s="21"/>
-      <c r="G714" s="22"/>
+      <c r="E714" s="23"/>
+      <c r="G714" s="24"/>
     </row>
     <row r="715">
-      <c r="E715" s="21"/>
-      <c r="G715" s="22"/>
+      <c r="E715" s="23"/>
+      <c r="G715" s="24"/>
     </row>
     <row r="716">
-      <c r="E716" s="21"/>
-      <c r="G716" s="22"/>
+      <c r="E716" s="23"/>
+      <c r="G716" s="24"/>
     </row>
     <row r="717">
-      <c r="E717" s="21"/>
-      <c r="G717" s="22"/>
+      <c r="E717" s="23"/>
+      <c r="G717" s="24"/>
     </row>
     <row r="718">
-      <c r="E718" s="21"/>
-      <c r="G718" s="22"/>
+      <c r="E718" s="23"/>
+      <c r="G718" s="24"/>
     </row>
     <row r="719">
-      <c r="E719" s="21"/>
-      <c r="G719" s="22"/>
+      <c r="E719" s="23"/>
+      <c r="G719" s="24"/>
     </row>
     <row r="720">
-      <c r="E720" s="21"/>
-      <c r="G720" s="22"/>
+      <c r="E720" s="23"/>
+      <c r="G720" s="24"/>
     </row>
     <row r="721">
-      <c r="E721" s="21"/>
-      <c r="G721" s="22"/>
+      <c r="E721" s="23"/>
+      <c r="G721" s="24"/>
     </row>
     <row r="722">
-      <c r="E722" s="21"/>
-      <c r="G722" s="22"/>
+      <c r="E722" s="23"/>
+      <c r="G722" s="24"/>
     </row>
     <row r="723">
-      <c r="E723" s="21"/>
-      <c r="G723" s="22"/>
+      <c r="E723" s="23"/>
+      <c r="G723" s="24"/>
     </row>
     <row r="724">
-      <c r="E724" s="21"/>
-      <c r="G724" s="22"/>
+      <c r="E724" s="23"/>
+      <c r="G724" s="24"/>
     </row>
     <row r="725">
-      <c r="E725" s="21"/>
-      <c r="G725" s="22"/>
+      <c r="E725" s="23"/>
+      <c r="G725" s="24"/>
     </row>
     <row r="726">
-      <c r="E726" s="21"/>
-      <c r="G726" s="22"/>
+      <c r="E726" s="23"/>
+      <c r="G726" s="24"/>
     </row>
     <row r="727">
-      <c r="E727" s="21"/>
-      <c r="G727" s="22"/>
+      <c r="E727" s="23"/>
+      <c r="G727" s="24"/>
     </row>
     <row r="728">
-      <c r="E728" s="21"/>
-      <c r="G728" s="22"/>
+      <c r="E728" s="23"/>
+      <c r="G728" s="24"/>
     </row>
     <row r="729">
-      <c r="E729" s="21"/>
-      <c r="G729" s="22"/>
+      <c r="E729" s="23"/>
+      <c r="G729" s="24"/>
     </row>
     <row r="730">
-      <c r="E730" s="21"/>
-      <c r="G730" s="22"/>
+      <c r="E730" s="23"/>
+      <c r="G730" s="24"/>
     </row>
     <row r="731">
-      <c r="E731" s="21"/>
-      <c r="G731" s="22"/>
+      <c r="E731" s="23"/>
+      <c r="G731" s="24"/>
     </row>
     <row r="732">
-      <c r="E732" s="21"/>
-      <c r="G732" s="22"/>
+      <c r="E732" s="23"/>
+      <c r="G732" s="24"/>
     </row>
     <row r="733">
-      <c r="E733" s="21"/>
-      <c r="G733" s="22"/>
+      <c r="E733" s="23"/>
+      <c r="G733" s="24"/>
     </row>
     <row r="734">
-      <c r="E734" s="21"/>
-      <c r="G734" s="22"/>
+      <c r="E734" s="23"/>
+      <c r="G734" s="24"/>
     </row>
     <row r="735">
-      <c r="E735" s="21"/>
-      <c r="G735" s="22"/>
+      <c r="E735" s="23"/>
+      <c r="G735" s="24"/>
     </row>
     <row r="736">
-      <c r="E736" s="21"/>
-      <c r="G736" s="22"/>
+      <c r="E736" s="23"/>
+      <c r="G736" s="24"/>
     </row>
     <row r="737">
-      <c r="E737" s="21"/>
-      <c r="G737" s="22"/>
+      <c r="E737" s="23"/>
+      <c r="G737" s="24"/>
     </row>
     <row r="738">
-      <c r="E738" s="21"/>
-      <c r="G738" s="22"/>
+      <c r="E738" s="23"/>
+      <c r="G738" s="24"/>
     </row>
     <row r="739">
-      <c r="E739" s="21"/>
-      <c r="G739" s="22"/>
+      <c r="E739" s="23"/>
+      <c r="G739" s="24"/>
     </row>
     <row r="740">
-      <c r="E740" s="21"/>
-      <c r="G740" s="22"/>
+      <c r="E740" s="23"/>
+      <c r="G740" s="24"/>
     </row>
     <row r="741">
-      <c r="E741" s="21"/>
-      <c r="G741" s="22"/>
+      <c r="E741" s="23"/>
+      <c r="G741" s="24"/>
     </row>
     <row r="742">
-      <c r="E742" s="21"/>
-      <c r="G742" s="22"/>
+      <c r="E742" s="23"/>
+      <c r="G742" s="24"/>
     </row>
     <row r="743">
-      <c r="E743" s="21"/>
-      <c r="G743" s="22"/>
+      <c r="E743" s="23"/>
+      <c r="G743" s="24"/>
     </row>
     <row r="744">
-      <c r="E744" s="21"/>
-      <c r="G744" s="22"/>
+      <c r="E744" s="23"/>
+      <c r="G744" s="24"/>
     </row>
     <row r="745">
-      <c r="E745" s="21"/>
-      <c r="G745" s="22"/>
+      <c r="E745" s="23"/>
+      <c r="G745" s="24"/>
     </row>
     <row r="746">
-      <c r="E746" s="21"/>
-      <c r="G746" s="22"/>
+      <c r="E746" s="23"/>
+      <c r="G746" s="24"/>
     </row>
     <row r="747">
-      <c r="E747" s="21"/>
-      <c r="G747" s="22"/>
+      <c r="E747" s="23"/>
+      <c r="G747" s="24"/>
     </row>
     <row r="748">
-      <c r="E748" s="21"/>
-      <c r="G748" s="22"/>
+      <c r="E748" s="23"/>
+      <c r="G748" s="24"/>
     </row>
     <row r="749">
-      <c r="E749" s="21"/>
-      <c r="G749" s="22"/>
+      <c r="E749" s="23"/>
+      <c r="G749" s="24"/>
     </row>
     <row r="750">
-      <c r="E750" s="21"/>
-      <c r="G750" s="22"/>
+      <c r="E750" s="23"/>
+      <c r="G750" s="24"/>
     </row>
     <row r="751">
-      <c r="E751" s="21"/>
-      <c r="G751" s="22"/>
+      <c r="E751" s="23"/>
+      <c r="G751" s="24"/>
     </row>
     <row r="752">
-      <c r="E752" s="21"/>
-      <c r="G752" s="22"/>
+      <c r="E752" s="23"/>
+      <c r="G752" s="24"/>
     </row>
     <row r="753">
-      <c r="E753" s="21"/>
-      <c r="G753" s="22"/>
+      <c r="E753" s="23"/>
+      <c r="G753" s="24"/>
     </row>
     <row r="754">
-      <c r="E754" s="21"/>
-      <c r="G754" s="22"/>
+      <c r="E754" s="23"/>
+      <c r="G754" s="24"/>
     </row>
     <row r="755">
-      <c r="E755" s="21"/>
-      <c r="G755" s="22"/>
+      <c r="E755" s="23"/>
+      <c r="G755" s="24"/>
     </row>
     <row r="756">
-      <c r="E756" s="21"/>
-      <c r="G756" s="22"/>
+      <c r="E756" s="23"/>
+      <c r="G756" s="24"/>
     </row>
     <row r="757">
-      <c r="E757" s="21"/>
-      <c r="G757" s="22"/>
+      <c r="E757" s="23"/>
+      <c r="G757" s="24"/>
     </row>
     <row r="758">
-      <c r="E758" s="21"/>
-      <c r="G758" s="22"/>
+      <c r="E758" s="23"/>
+      <c r="G758" s="24"/>
     </row>
     <row r="759">
-      <c r="E759" s="21"/>
-      <c r="G759" s="22"/>
+      <c r="E759" s="23"/>
+      <c r="G759" s="24"/>
     </row>
     <row r="760">
-      <c r="E760" s="21"/>
-      <c r="G760" s="22"/>
+      <c r="E760" s="23"/>
+      <c r="G760" s="24"/>
     </row>
     <row r="761">
-      <c r="E761" s="21"/>
-      <c r="G761" s="22"/>
+      <c r="E761" s="23"/>
+      <c r="G761" s="24"/>
     </row>
     <row r="762">
-      <c r="E762" s="21"/>
-      <c r="G762" s="22"/>
+      <c r="E762" s="23"/>
+      <c r="G762" s="24"/>
     </row>
     <row r="763">
-      <c r="E763" s="21"/>
-      <c r="G763" s="22"/>
+      <c r="E763" s="23"/>
+      <c r="G763" s="24"/>
     </row>
     <row r="764">
-      <c r="E764" s="21"/>
-      <c r="G764" s="22"/>
+      <c r="E764" s="23"/>
+      <c r="G764" s="24"/>
     </row>
     <row r="765">
-      <c r="E765" s="21"/>
-      <c r="G765" s="22"/>
+      <c r="E765" s="23"/>
+      <c r="G765" s="24"/>
     </row>
     <row r="766">
-      <c r="E766" s="21"/>
-      <c r="G766" s="22"/>
+      <c r="E766" s="23"/>
+      <c r="G766" s="24"/>
     </row>
     <row r="767">
-      <c r="E767" s="21"/>
-      <c r="G767" s="22"/>
+      <c r="E767" s="23"/>
+      <c r="G767" s="24"/>
     </row>
     <row r="768">
-      <c r="E768" s="21"/>
-      <c r="G768" s="22"/>
+      <c r="E768" s="23"/>
+      <c r="G768" s="24"/>
     </row>
     <row r="769">
-      <c r="E769" s="21"/>
-      <c r="G769" s="22"/>
+      <c r="E769" s="23"/>
+      <c r="G769" s="24"/>
     </row>
     <row r="770">
-      <c r="E770" s="21"/>
-      <c r="G770" s="22"/>
+      <c r="E770" s="23"/>
+      <c r="G770" s="24"/>
     </row>
     <row r="771">
-      <c r="E771" s="21"/>
-      <c r="G771" s="22"/>
+      <c r="E771" s="23"/>
+      <c r="G771" s="24"/>
     </row>
     <row r="772">
-      <c r="E772" s="21"/>
-      <c r="G772" s="22"/>
+      <c r="E772" s="23"/>
+      <c r="G772" s="24"/>
     </row>
     <row r="773">
-      <c r="E773" s="21"/>
-      <c r="G773" s="22"/>
+      <c r="E773" s="23"/>
+      <c r="G773" s="24"/>
     </row>
     <row r="774">
-      <c r="E774" s="21"/>
-      <c r="G774" s="22"/>
+      <c r="E774" s="23"/>
+      <c r="G774" s="24"/>
     </row>
     <row r="775">
-      <c r="E775" s="21"/>
-      <c r="G775" s="22"/>
+      <c r="E775" s="23"/>
+      <c r="G775" s="24"/>
     </row>
     <row r="776">
-      <c r="E776" s="21"/>
-      <c r="G776" s="22"/>
+      <c r="E776" s="23"/>
+      <c r="G776" s="24"/>
     </row>
     <row r="777">
-      <c r="E777" s="21"/>
-      <c r="G777" s="22"/>
+      <c r="E777" s="23"/>
+      <c r="G777" s="24"/>
     </row>
     <row r="778">
-      <c r="E778" s="21"/>
-      <c r="G778" s="22"/>
+      <c r="E778" s="23"/>
+      <c r="G778" s="24"/>
     </row>
     <row r="779">
-      <c r="E779" s="21"/>
-      <c r="G779" s="22"/>
+      <c r="E779" s="23"/>
+      <c r="G779" s="24"/>
     </row>
     <row r="780">
-      <c r="E780" s="21"/>
-      <c r="G780" s="22"/>
+      <c r="E780" s="23"/>
+      <c r="G780" s="24"/>
     </row>
     <row r="781">
-      <c r="E781" s="21"/>
-      <c r="G781" s="22"/>
+      <c r="E781" s="23"/>
+      <c r="G781" s="24"/>
     </row>
     <row r="782">
-      <c r="E782" s="21"/>
-      <c r="G782" s="22"/>
+      <c r="E782" s="23"/>
+      <c r="G782" s="24"/>
     </row>
     <row r="783">
-      <c r="E783" s="21"/>
-      <c r="G783" s="22"/>
+      <c r="E783" s="23"/>
+      <c r="G783" s="24"/>
     </row>
     <row r="784">
-      <c r="E784" s="21"/>
-      <c r="G784" s="22"/>
+      <c r="E784" s="23"/>
+      <c r="G784" s="24"/>
     </row>
     <row r="785">
-      <c r="E785" s="21"/>
-      <c r="G785" s="22"/>
+      <c r="E785" s="23"/>
+      <c r="G785" s="24"/>
     </row>
     <row r="786">
-      <c r="E786" s="21"/>
-      <c r="G786" s="22"/>
+      <c r="E786" s="23"/>
+      <c r="G786" s="24"/>
     </row>
     <row r="787">
-      <c r="E787" s="21"/>
-      <c r="G787" s="22"/>
+      <c r="E787" s="23"/>
+      <c r="G787" s="24"/>
     </row>
     <row r="788">
-      <c r="E788" s="21"/>
-      <c r="G788" s="22"/>
+      <c r="E788" s="23"/>
+      <c r="G788" s="24"/>
     </row>
     <row r="789">
-      <c r="E789" s="21"/>
-      <c r="G789" s="22"/>
+      <c r="E789" s="23"/>
+      <c r="G789" s="24"/>
     </row>
     <row r="790">
-      <c r="E790" s="21"/>
-      <c r="G790" s="22"/>
+      <c r="E790" s="23"/>
+      <c r="G790" s="24"/>
     </row>
     <row r="791">
-      <c r="E791" s="21"/>
-      <c r="G791" s="22"/>
+      <c r="E791" s="23"/>
+      <c r="G791" s="24"/>
     </row>
     <row r="792">
-      <c r="E792" s="21"/>
-      <c r="G792" s="22"/>
+      <c r="E792" s="23"/>
+      <c r="G792" s="24"/>
     </row>
     <row r="793">
-      <c r="E793" s="21"/>
-      <c r="G793" s="22"/>
+      <c r="E793" s="23"/>
+      <c r="G793" s="24"/>
     </row>
     <row r="794">
-      <c r="E794" s="21"/>
-      <c r="G794" s="22"/>
+      <c r="E794" s="23"/>
+      <c r="G794" s="24"/>
     </row>
     <row r="795">
-      <c r="E795" s="21"/>
-      <c r="G795" s="22"/>
+      <c r="E795" s="23"/>
+      <c r="G795" s="24"/>
     </row>
     <row r="796">
-      <c r="E796" s="21"/>
-      <c r="G796" s="22"/>
+      <c r="E796" s="23"/>
+      <c r="G796" s="24"/>
     </row>
     <row r="797">
-      <c r="E797" s="21"/>
-      <c r="G797" s="22"/>
+      <c r="E797" s="23"/>
+      <c r="G797" s="24"/>
     </row>
     <row r="798">
-      <c r="E798" s="21"/>
-      <c r="G798" s="22"/>
+      <c r="E798" s="23"/>
+      <c r="G798" s="24"/>
     </row>
     <row r="799">
-      <c r="E799" s="21"/>
-      <c r="G799" s="22"/>
+      <c r="E799" s="23"/>
+      <c r="G799" s="24"/>
     </row>
     <row r="800">
-      <c r="E800" s="21"/>
-      <c r="G800" s="22"/>
+      <c r="E800" s="23"/>
+      <c r="G800" s="24"/>
     </row>
     <row r="801">
-      <c r="E801" s="21"/>
-      <c r="G801" s="22"/>
+      <c r="E801" s="23"/>
+      <c r="G801" s="24"/>
     </row>
     <row r="802">
-      <c r="E802" s="21"/>
-      <c r="G802" s="22"/>
+      <c r="E802" s="23"/>
+      <c r="G802" s="24"/>
     </row>
     <row r="803">
-      <c r="E803" s="21"/>
-      <c r="G803" s="22"/>
+      <c r="E803" s="23"/>
+      <c r="G803" s="24"/>
     </row>
     <row r="804">
-      <c r="E804" s="21"/>
-      <c r="G804" s="22"/>
+      <c r="E804" s="23"/>
+      <c r="G804" s="24"/>
     </row>
     <row r="805">
-      <c r="E805" s="21"/>
-      <c r="G805" s="22"/>
+      <c r="E805" s="23"/>
+      <c r="G805" s="24"/>
     </row>
     <row r="806">
-      <c r="E806" s="21"/>
-      <c r="G806" s="22"/>
+      <c r="E806" s="23"/>
+      <c r="G806" s="24"/>
     </row>
     <row r="807">
-      <c r="E807" s="21"/>
-      <c r="G807" s="22"/>
+      <c r="E807" s="23"/>
+      <c r="G807" s="24"/>
     </row>
     <row r="808">
-      <c r="E808" s="21"/>
-      <c r="G808" s="22"/>
+      <c r="E808" s="23"/>
+      <c r="G808" s="24"/>
     </row>
     <row r="809">
-      <c r="E809" s="21"/>
-      <c r="G809" s="22"/>
+      <c r="E809" s="23"/>
+      <c r="G809" s="24"/>
     </row>
     <row r="810">
-      <c r="E810" s="21"/>
-      <c r="G810" s="22"/>
+      <c r="E810" s="23"/>
+      <c r="G810" s="24"/>
     </row>
     <row r="811">
-      <c r="E811" s="21"/>
-      <c r="G811" s="22"/>
+      <c r="E811" s="23"/>
+      <c r="G811" s="24"/>
     </row>
     <row r="812">
-      <c r="E812" s="21"/>
-      <c r="G812" s="22"/>
+      <c r="E812" s="23"/>
+      <c r="G812" s="24"/>
     </row>
     <row r="813">
-      <c r="E813" s="21"/>
-      <c r="G813" s="22"/>
+      <c r="E813" s="23"/>
+      <c r="G813" s="24"/>
     </row>
     <row r="814">
-      <c r="E814" s="21"/>
-      <c r="G814" s="22"/>
+      <c r="E814" s="23"/>
+      <c r="G814" s="24"/>
     </row>
     <row r="815">
-      <c r="E815" s="21"/>
-      <c r="G815" s="22"/>
+      <c r="E815" s="23"/>
+      <c r="G815" s="24"/>
     </row>
     <row r="816">
-      <c r="E816" s="21"/>
-      <c r="G816" s="22"/>
+      <c r="E816" s="23"/>
+      <c r="G816" s="24"/>
     </row>
     <row r="817">
-      <c r="E817" s="21"/>
-      <c r="G817" s="22"/>
+      <c r="E817" s="23"/>
+      <c r="G817" s="24"/>
     </row>
     <row r="818">
-      <c r="E818" s="21"/>
-      <c r="G818" s="22"/>
+      <c r="E818" s="23"/>
+      <c r="G818" s="24"/>
     </row>
     <row r="819">
-      <c r="E819" s="21"/>
-      <c r="G819" s="22"/>
+      <c r="E819" s="23"/>
+      <c r="G819" s="24"/>
     </row>
     <row r="820">
-      <c r="E820" s="21"/>
-      <c r="G820" s="22"/>
+      <c r="E820" s="23"/>
+      <c r="G820" s="24"/>
     </row>
     <row r="821">
-      <c r="E821" s="21"/>
-      <c r="G821" s="22"/>
+      <c r="E821" s="23"/>
+      <c r="G821" s="24"/>
     </row>
     <row r="822">
-      <c r="E822" s="21"/>
-      <c r="G822" s="22"/>
+      <c r="E822" s="23"/>
+      <c r="G822" s="24"/>
     </row>
     <row r="823">
-      <c r="E823" s="21"/>
-      <c r="G823" s="22"/>
+      <c r="E823" s="23"/>
+      <c r="G823" s="24"/>
     </row>
     <row r="824">
-      <c r="E824" s="21"/>
-      <c r="G824" s="22"/>
+      <c r="E824" s="23"/>
+      <c r="G824" s="24"/>
     </row>
     <row r="825">
-      <c r="E825" s="21"/>
-      <c r="G825" s="22"/>
+      <c r="E825" s="23"/>
+      <c r="G825" s="24"/>
     </row>
     <row r="826">
-      <c r="E826" s="21"/>
-      <c r="G826" s="22"/>
+      <c r="E826" s="23"/>
+      <c r="G826" s="24"/>
     </row>
     <row r="827">
-      <c r="E827" s="21"/>
-      <c r="G827" s="22"/>
+      <c r="E827" s="23"/>
+      <c r="G827" s="24"/>
     </row>
     <row r="828">
-      <c r="E828" s="21"/>
-      <c r="G828" s="22"/>
+      <c r="E828" s="23"/>
+      <c r="G828" s="24"/>
     </row>
     <row r="829">
-      <c r="E829" s="21"/>
-      <c r="G829" s="22"/>
+      <c r="E829" s="23"/>
+      <c r="G829" s="24"/>
     </row>
     <row r="830">
-      <c r="E830" s="21"/>
-      <c r="G830" s="22"/>
+      <c r="E830" s="23"/>
+      <c r="G830" s="24"/>
     </row>
     <row r="831">
-      <c r="E831" s="21"/>
-      <c r="G831" s="22"/>
+      <c r="E831" s="23"/>
+      <c r="G831" s="24"/>
     </row>
     <row r="832">
-      <c r="E832" s="21"/>
-      <c r="G832" s="22"/>
+      <c r="E832" s="23"/>
+      <c r="G832" s="24"/>
     </row>
     <row r="833">
-      <c r="E833" s="21"/>
-      <c r="G833" s="22"/>
+      <c r="E833" s="23"/>
+      <c r="G833" s="24"/>
     </row>
     <row r="834">
-      <c r="E834" s="21"/>
-      <c r="G834" s="22"/>
+      <c r="E834" s="23"/>
+      <c r="G834" s="24"/>
     </row>
     <row r="835">
-      <c r="E835" s="21"/>
-      <c r="G835" s="22"/>
+      <c r="E835" s="23"/>
+      <c r="G835" s="24"/>
     </row>
     <row r="836">
-      <c r="E836" s="21"/>
-      <c r="G836" s="22"/>
+      <c r="E836" s="23"/>
+      <c r="G836" s="24"/>
     </row>
     <row r="837">
-      <c r="E837" s="21"/>
-      <c r="G837" s="22"/>
+      <c r="E837" s="23"/>
+      <c r="G837" s="24"/>
     </row>
     <row r="838">
-      <c r="E838" s="21"/>
-      <c r="G838" s="22"/>
+      <c r="E838" s="23"/>
+      <c r="G838" s="24"/>
     </row>
     <row r="839">
-      <c r="E839" s="21"/>
-      <c r="G839" s="22"/>
+      <c r="E839" s="23"/>
+      <c r="G839" s="24"/>
     </row>
     <row r="840">
-      <c r="E840" s="21"/>
-      <c r="G840" s="22"/>
+      <c r="E840" s="23"/>
+      <c r="G840" s="24"/>
     </row>
     <row r="841">
-      <c r="E841" s="21"/>
-      <c r="G841" s="22"/>
+      <c r="E841" s="23"/>
+      <c r="G841" s="24"/>
     </row>
     <row r="842">
-      <c r="E842" s="21"/>
-      <c r="G842" s="22"/>
+      <c r="E842" s="23"/>
+      <c r="G842" s="24"/>
     </row>
     <row r="843">
-      <c r="E843" s="21"/>
-      <c r="G843" s="22"/>
+      <c r="E843" s="23"/>
+      <c r="G843" s="24"/>
     </row>
     <row r="844">
-      <c r="E844" s="21"/>
-      <c r="G844" s="22"/>
+      <c r="E844" s="23"/>
+      <c r="G844" s="24"/>
     </row>
     <row r="845">
-      <c r="E845" s="21"/>
-      <c r="G845" s="22"/>
+      <c r="E845" s="23"/>
+      <c r="G845" s="24"/>
     </row>
     <row r="846">
-      <c r="E846" s="21"/>
-      <c r="G846" s="22"/>
+      <c r="E846" s="23"/>
+      <c r="G846" s="24"/>
     </row>
     <row r="847">
-      <c r="E847" s="21"/>
-      <c r="G847" s="22"/>
+      <c r="E847" s="23"/>
+      <c r="G847" s="24"/>
     </row>
     <row r="848">
-      <c r="E848" s="21"/>
-      <c r="G848" s="22"/>
+      <c r="E848" s="23"/>
+      <c r="G848" s="24"/>
     </row>
     <row r="849">
-      <c r="E849" s="21"/>
-      <c r="G849" s="22"/>
+      <c r="E849" s="23"/>
+      <c r="G849" s="24"/>
     </row>
     <row r="850">
-      <c r="E850" s="21"/>
-      <c r="G850" s="22"/>
+      <c r="E850" s="23"/>
+      <c r="G850" s="24"/>
     </row>
     <row r="851">
-      <c r="E851" s="21"/>
-      <c r="G851" s="22"/>
+      <c r="E851" s="23"/>
+      <c r="G851" s="24"/>
     </row>
     <row r="852">
-      <c r="E852" s="21"/>
-      <c r="G852" s="22"/>
+      <c r="E852" s="23"/>
+      <c r="G852" s="24"/>
     </row>
     <row r="853">
-      <c r="E853" s="21"/>
-      <c r="G853" s="22"/>
+      <c r="E853" s="23"/>
+      <c r="G853" s="24"/>
     </row>
     <row r="854">
-      <c r="E854" s="21"/>
-      <c r="G854" s="22"/>
+      <c r="E854" s="23"/>
+      <c r="G854" s="24"/>
     </row>
     <row r="855">
-      <c r="E855" s="21"/>
-      <c r="G855" s="22"/>
+      <c r="E855" s="23"/>
+      <c r="G855" s="24"/>
     </row>
     <row r="856">
-      <c r="E856" s="21"/>
-      <c r="G856" s="22"/>
+      <c r="E856" s="23"/>
+      <c r="G856" s="24"/>
     </row>
     <row r="857">
-      <c r="E857" s="21"/>
-      <c r="G857" s="22"/>
+      <c r="E857" s="23"/>
+      <c r="G857" s="24"/>
     </row>
     <row r="858">
-      <c r="E858" s="21"/>
-      <c r="G858" s="22"/>
+      <c r="E858" s="23"/>
+      <c r="G858" s="24"/>
     </row>
     <row r="859">
-      <c r="E859" s="21"/>
-      <c r="G859" s="22"/>
+      <c r="E859" s="23"/>
+      <c r="G859" s="24"/>
     </row>
     <row r="860">
-      <c r="E860" s="21"/>
-      <c r="G860" s="22"/>
+      <c r="E860" s="23"/>
+      <c r="G860" s="24"/>
     </row>
     <row r="861">
-      <c r="E861" s="21"/>
-      <c r="G861" s="22"/>
+      <c r="E861" s="23"/>
+      <c r="G861" s="24"/>
     </row>
     <row r="862">
-      <c r="E862" s="21"/>
-      <c r="G862" s="22"/>
+      <c r="E862" s="23"/>
+      <c r="G862" s="24"/>
     </row>
     <row r="863">
-      <c r="E863" s="21"/>
-      <c r="G863" s="22"/>
+      <c r="E863" s="23"/>
+      <c r="G863" s="24"/>
     </row>
     <row r="864">
-      <c r="E864" s="21"/>
-      <c r="G864" s="22"/>
+      <c r="E864" s="23"/>
+      <c r="G864" s="24"/>
     </row>
     <row r="865">
-      <c r="E865" s="21"/>
-      <c r="G865" s="22"/>
+      <c r="E865" s="23"/>
+      <c r="G865" s="24"/>
     </row>
     <row r="866">
-      <c r="E866" s="21"/>
-      <c r="G866" s="22"/>
+      <c r="E866" s="23"/>
+      <c r="G866" s="24"/>
     </row>
     <row r="867">
-      <c r="E867" s="21"/>
-      <c r="G867" s="22"/>
+      <c r="E867" s="23"/>
+      <c r="G867" s="24"/>
     </row>
     <row r="868">
-      <c r="E868" s="21"/>
-      <c r="G868" s="22"/>
+      <c r="E868" s="23"/>
+      <c r="G868" s="24"/>
     </row>
     <row r="869">
-      <c r="E869" s="21"/>
-      <c r="G869" s="22"/>
+      <c r="E869" s="23"/>
+      <c r="G869" s="24"/>
     </row>
     <row r="870">
-      <c r="E870" s="21"/>
-      <c r="G870" s="22"/>
+      <c r="E870" s="23"/>
+      <c r="G870" s="24"/>
     </row>
     <row r="871">
-      <c r="E871" s="21"/>
-      <c r="G871" s="22"/>
+      <c r="E871" s="23"/>
+      <c r="G871" s="24"/>
     </row>
     <row r="872">
-      <c r="E872" s="21"/>
-      <c r="G872" s="22"/>
+      <c r="E872" s="23"/>
+      <c r="G872" s="24"/>
     </row>
     <row r="873">
-      <c r="E873" s="21"/>
-      <c r="G873" s="22"/>
+      <c r="E873" s="23"/>
+      <c r="G873" s="24"/>
     </row>
     <row r="874">
-      <c r="E874" s="21"/>
-      <c r="G874" s="22"/>
+      <c r="E874" s="23"/>
+      <c r="G874" s="24"/>
     </row>
     <row r="875">
-      <c r="E875" s="21"/>
-      <c r="G875" s="22"/>
+      <c r="E875" s="23"/>
+      <c r="G875" s="24"/>
     </row>
     <row r="876">
-      <c r="E876" s="21"/>
-      <c r="G876" s="22"/>
+      <c r="E876" s="23"/>
+      <c r="G876" s="24"/>
     </row>
     <row r="877">
-      <c r="E877" s="21"/>
-      <c r="G877" s="22"/>
+      <c r="E877" s="23"/>
+      <c r="G877" s="24"/>
     </row>
     <row r="878">
-      <c r="E878" s="21"/>
-      <c r="G878" s="22"/>
+      <c r="E878" s="23"/>
+      <c r="G878" s="24"/>
     </row>
     <row r="879">
-      <c r="E879" s="21"/>
-      <c r="G879" s="22"/>
+      <c r="E879" s="23"/>
+      <c r="G879" s="24"/>
     </row>
     <row r="880">
-      <c r="E880" s="21"/>
-      <c r="G880" s="22"/>
+      <c r="E880" s="23"/>
+      <c r="G880" s="24"/>
     </row>
     <row r="881">
-      <c r="E881" s="21"/>
-      <c r="G881" s="22"/>
+      <c r="E881" s="23"/>
+      <c r="G881" s="24"/>
     </row>
     <row r="882">
-      <c r="E882" s="21"/>
-      <c r="G882" s="22"/>
+      <c r="E882" s="23"/>
+      <c r="G882" s="24"/>
     </row>
     <row r="883">
-      <c r="E883" s="21"/>
-      <c r="G883" s="22"/>
+      <c r="E883" s="23"/>
+      <c r="G883" s="24"/>
     </row>
     <row r="884">
-      <c r="E884" s="21"/>
-      <c r="G884" s="22"/>
+      <c r="E884" s="23"/>
+      <c r="G884" s="24"/>
     </row>
     <row r="885">
-      <c r="E885" s="21"/>
-      <c r="G885" s="22"/>
+      <c r="E885" s="23"/>
+      <c r="G885" s="24"/>
     </row>
     <row r="886">
-      <c r="E886" s="21"/>
-      <c r="G886" s="22"/>
+      <c r="E886" s="23"/>
+      <c r="G886" s="24"/>
     </row>
     <row r="887">
-      <c r="E887" s="21"/>
-      <c r="G887" s="22"/>
+      <c r="E887" s="23"/>
+      <c r="G887" s="24"/>
     </row>
     <row r="888">
-      <c r="E888" s="21"/>
-      <c r="G888" s="22"/>
+      <c r="E888" s="23"/>
+      <c r="G888" s="24"/>
     </row>
     <row r="889">
-      <c r="E889" s="21"/>
-      <c r="G889" s="22"/>
+      <c r="E889" s="23"/>
+      <c r="G889" s="24"/>
     </row>
     <row r="890">
-      <c r="E890" s="21"/>
-      <c r="G890" s="22"/>
+      <c r="E890" s="23"/>
+      <c r="G890" s="24"/>
     </row>
     <row r="891">
-      <c r="E891" s="21"/>
-      <c r="G891" s="22"/>
+      <c r="E891" s="23"/>
+      <c r="G891" s="24"/>
     </row>
     <row r="892">
-      <c r="E892" s="21"/>
-      <c r="G892" s="22"/>
+      <c r="E892" s="23"/>
+      <c r="G892" s="24"/>
     </row>
     <row r="893">
-      <c r="E893" s="21"/>
-      <c r="G893" s="22"/>
+      <c r="E893" s="23"/>
+      <c r="G893" s="24"/>
     </row>
     <row r="894">
-      <c r="E894" s="21"/>
-      <c r="G894" s="22"/>
+      <c r="E894" s="23"/>
+      <c r="G894" s="24"/>
     </row>
     <row r="895">
-      <c r="E895" s="21"/>
-      <c r="G895" s="22"/>
+      <c r="E895" s="23"/>
+      <c r="G895" s="24"/>
     </row>
     <row r="896">
-      <c r="E896" s="21"/>
-      <c r="G896" s="22"/>
+      <c r="E896" s="23"/>
+      <c r="G896" s="24"/>
     </row>
     <row r="897">
-      <c r="E897" s="21"/>
-      <c r="G897" s="22"/>
+      <c r="E897" s="23"/>
+      <c r="G897" s="24"/>
     </row>
     <row r="898">
-      <c r="E898" s="21"/>
-      <c r="G898" s="22"/>
+      <c r="E898" s="23"/>
+      <c r="G898" s="24"/>
     </row>
     <row r="899">
-      <c r="E899" s="21"/>
-      <c r="G899" s="22"/>
+      <c r="E899" s="23"/>
+      <c r="G899" s="24"/>
     </row>
     <row r="900">
-      <c r="E900" s="21"/>
-      <c r="G900" s="22"/>
+      <c r="E900" s="23"/>
+      <c r="G900" s="24"/>
     </row>
     <row r="901">
-      <c r="E901" s="21"/>
-      <c r="G901" s="22"/>
+      <c r="E901" s="23"/>
+      <c r="G901" s="24"/>
     </row>
     <row r="902">
-      <c r="E902" s="21"/>
-      <c r="G902" s="22"/>
+      <c r="E902" s="23"/>
+      <c r="G902" s="24"/>
     </row>
     <row r="903">
-      <c r="E903" s="21"/>
-      <c r="G903" s="22"/>
+      <c r="E903" s="23"/>
+      <c r="G903" s="24"/>
     </row>
     <row r="904">
-      <c r="E904" s="21"/>
-      <c r="G904" s="22"/>
+      <c r="E904" s="23"/>
+      <c r="G904" s="24"/>
     </row>
     <row r="905">
-      <c r="E905" s="21"/>
-      <c r="G905" s="22"/>
+      <c r="E905" s="23"/>
+      <c r="G905" s="24"/>
     </row>
     <row r="906">
-      <c r="E906" s="21"/>
-      <c r="G906" s="22"/>
+      <c r="E906" s="23"/>
+      <c r="G906" s="24"/>
     </row>
     <row r="907">
-      <c r="E907" s="21"/>
-      <c r="G907" s="22"/>
+      <c r="E907" s="23"/>
+      <c r="G907" s="24"/>
     </row>
     <row r="908">
-      <c r="E908" s="21"/>
-      <c r="G908" s="22"/>
+      <c r="E908" s="23"/>
+      <c r="G908" s="24"/>
     </row>
     <row r="909">
-      <c r="E909" s="21"/>
-      <c r="G909" s="22"/>
+      <c r="E909" s="23"/>
+      <c r="G909" s="24"/>
     </row>
     <row r="910">
-      <c r="E910" s="21"/>
-      <c r="G910" s="22"/>
+      <c r="E910" s="23"/>
+      <c r="G910" s="24"/>
     </row>
     <row r="911">
-      <c r="E911" s="21"/>
-      <c r="G911" s="22"/>
+      <c r="E911" s="23"/>
+      <c r="G911" s="24"/>
     </row>
     <row r="912">
-      <c r="E912" s="21"/>
-      <c r="G912" s="22"/>
+      <c r="E912" s="23"/>
+      <c r="G912" s="24"/>
     </row>
     <row r="913">
-      <c r="E913" s="21"/>
-      <c r="G913" s="22"/>
+      <c r="E913" s="23"/>
+      <c r="G913" s="24"/>
     </row>
     <row r="914">
-      <c r="E914" s="21"/>
-      <c r="G914" s="22"/>
+      <c r="E914" s="23"/>
+      <c r="G914" s="24"/>
     </row>
     <row r="915">
-      <c r="E915" s="21"/>
-      <c r="G915" s="22"/>
+      <c r="E915" s="23"/>
+      <c r="G915" s="24"/>
     </row>
     <row r="916">
-      <c r="E916" s="21"/>
-      <c r="G916" s="22"/>
+      <c r="E916" s="23"/>
+      <c r="G916" s="24"/>
     </row>
     <row r="917">
-      <c r="E917" s="21"/>
-      <c r="G917" s="22"/>
+      <c r="E917" s="23"/>
+      <c r="G917" s="24"/>
     </row>
     <row r="918">
-      <c r="E918" s="21"/>
-      <c r="G918" s="22"/>
+      <c r="E918" s="23"/>
+      <c r="G918" s="24"/>
     </row>
     <row r="919">
-      <c r="E919" s="21"/>
-      <c r="G919" s="22"/>
+      <c r="E919" s="23"/>
+      <c r="G919" s="24"/>
     </row>
     <row r="920">
-      <c r="E920" s="21"/>
-      <c r="G920" s="22"/>
+      <c r="E920" s="23"/>
+      <c r="G920" s="24"/>
     </row>
     <row r="921">
-      <c r="E921" s="21"/>
-      <c r="G921" s="22"/>
+      <c r="E921" s="23"/>
+      <c r="G921" s="24"/>
     </row>
     <row r="922">
-      <c r="E922" s="21"/>
-      <c r="G922" s="22"/>
+      <c r="E922" s="23"/>
+      <c r="G922" s="24"/>
     </row>
     <row r="923">
-      <c r="E923" s="21"/>
-      <c r="G923" s="22"/>
+      <c r="E923" s="23"/>
+      <c r="G923" s="24"/>
     </row>
     <row r="924">
-      <c r="E924" s="21"/>
-      <c r="G924" s="22"/>
+      <c r="E924" s="23"/>
+      <c r="G924" s="24"/>
     </row>
     <row r="925">
-      <c r="E925" s="21"/>
-      <c r="G925" s="22"/>
+      <c r="E925" s="23"/>
+      <c r="G925" s="24"/>
     </row>
     <row r="926">
-      <c r="E926" s="21"/>
-      <c r="G926" s="22"/>
+      <c r="E926" s="23"/>
+      <c r="G926" s="24"/>
     </row>
     <row r="927">
-      <c r="E927" s="21"/>
-      <c r="G927" s="22"/>
+      <c r="E927" s="23"/>
+      <c r="G927" s="24"/>
     </row>
     <row r="928">
-      <c r="E928" s="21"/>
-      <c r="G928" s="22"/>
+      <c r="E928" s="23"/>
+      <c r="G928" s="24"/>
     </row>
     <row r="929">
-      <c r="E929" s="21"/>
-      <c r="G929" s="22"/>
+      <c r="E929" s="23"/>
+      <c r="G929" s="24"/>
     </row>
     <row r="930">
-      <c r="E930" s="21"/>
-      <c r="G930" s="22"/>
+      <c r="E930" s="23"/>
+      <c r="G930" s="24"/>
     </row>
     <row r="931">
-      <c r="E931" s="21"/>
-      <c r="G931" s="22"/>
+      <c r="E931" s="23"/>
+      <c r="G931" s="24"/>
     </row>
     <row r="932">
-      <c r="E932" s="21"/>
-      <c r="G932" s="22"/>
+      <c r="E932" s="23"/>
+      <c r="G932" s="24"/>
     </row>
     <row r="933">
-      <c r="E933" s="21"/>
-      <c r="G933" s="22"/>
+      <c r="E933" s="23"/>
+      <c r="G933" s="24"/>
     </row>
     <row r="934">
-      <c r="E934" s="21"/>
-      <c r="G934" s="22"/>
+      <c r="E934" s="23"/>
+      <c r="G934" s="24"/>
     </row>
     <row r="935">
-      <c r="E935" s="21"/>
-      <c r="G935" s="22"/>
+      <c r="E935" s="23"/>
+      <c r="G935" s="24"/>
     </row>
     <row r="936">
-      <c r="E936" s="21"/>
-      <c r="G936" s="22"/>
+      <c r="E936" s="23"/>
+      <c r="G936" s="24"/>
     </row>
     <row r="937">
-      <c r="E937" s="21"/>
-      <c r="G937" s="22"/>
+      <c r="E937" s="23"/>
+      <c r="G937" s="24"/>
     </row>
     <row r="938">
-      <c r="E938" s="21"/>
-      <c r="G938" s="22"/>
+      <c r="E938" s="23"/>
+      <c r="G938" s="24"/>
     </row>
     <row r="939">
-      <c r="E939" s="21"/>
-      <c r="G939" s="22"/>
+      <c r="E939" s="23"/>
+      <c r="G939" s="24"/>
     </row>
     <row r="940">
-      <c r="E940" s="21"/>
-      <c r="G940" s="22"/>
+      <c r="E940" s="23"/>
+      <c r="G940" s="24"/>
     </row>
     <row r="941">
-      <c r="E941" s="21"/>
-      <c r="G941" s="22"/>
+      <c r="E941" s="23"/>
+      <c r="G941" s="24"/>
     </row>
     <row r="942">
-      <c r="E942" s="21"/>
-      <c r="G942" s="22"/>
+      <c r="E942" s="23"/>
+      <c r="G942" s="24"/>
     </row>
     <row r="943">
-      <c r="E943" s="21"/>
-      <c r="G943" s="22"/>
+      <c r="E943" s="23"/>
+      <c r="G943" s="24"/>
     </row>
     <row r="944">
-      <c r="E944" s="21"/>
-      <c r="G944" s="22"/>
+      <c r="E944" s="23"/>
+      <c r="G944" s="24"/>
     </row>
     <row r="945">
-      <c r="E945" s="21"/>
-      <c r="G945" s="22"/>
+      <c r="E945" s="23"/>
+      <c r="G945" s="24"/>
     </row>
     <row r="946">
-      <c r="E946" s="21"/>
-      <c r="G946" s="22"/>
+      <c r="E946" s="23"/>
+      <c r="G946" s="24"/>
     </row>
     <row r="947">
-      <c r="E947" s="21"/>
-      <c r="G947" s="22"/>
+      <c r="E947" s="23"/>
+      <c r="G947" s="24"/>
     </row>
     <row r="948">
-      <c r="E948" s="21"/>
-      <c r="G948" s="22"/>
+      <c r="E948" s="23"/>
+      <c r="G948" s="24"/>
     </row>
     <row r="949">
-      <c r="E949" s="21"/>
-      <c r="G949" s="22"/>
+      <c r="E949" s="23"/>
+      <c r="G949" s="24"/>
     </row>
     <row r="950">
-      <c r="E950" s="21"/>
-      <c r="G950" s="22"/>
+      <c r="E950" s="23"/>
+      <c r="G950" s="24"/>
     </row>
     <row r="951">
-      <c r="E951" s="21"/>
-      <c r="G951" s="22"/>
+      <c r="E951" s="23"/>
+      <c r="G951" s="24"/>
     </row>
     <row r="952">
-      <c r="E952" s="21"/>
-      <c r="G952" s="22"/>
+      <c r="E952" s="23"/>
+      <c r="G952" s="24"/>
     </row>
     <row r="953">
-      <c r="E953" s="21"/>
-      <c r="G953" s="22"/>
+      <c r="E953" s="23"/>
+      <c r="G953" s="24"/>
     </row>
     <row r="954">
-      <c r="E954" s="21"/>
-      <c r="G954" s="22"/>
+      <c r="E954" s="23"/>
+      <c r="G954" s="24"/>
     </row>
     <row r="955">
-      <c r="E955" s="21"/>
-      <c r="G955" s="22"/>
+      <c r="E955" s="23"/>
+      <c r="G955" s="24"/>
     </row>
     <row r="956">
-      <c r="E956" s="21"/>
-      <c r="G956" s="22"/>
+      <c r="E956" s="23"/>
+      <c r="G956" s="24"/>
     </row>
     <row r="957">
-      <c r="E957" s="21"/>
-      <c r="G957" s="22"/>
+      <c r="E957" s="23"/>
+      <c r="G957" s="24"/>
     </row>
     <row r="958">
-      <c r="E958" s="21"/>
-      <c r="G958" s="22"/>
+      <c r="E958" s="23"/>
+      <c r="G958" s="24"/>
     </row>
     <row r="959">
-      <c r="E959" s="21"/>
-      <c r="G959" s="22"/>
+      <c r="E959" s="23"/>
+      <c r="G959" s="24"/>
     </row>
     <row r="960">
-      <c r="E960" s="21"/>
-      <c r="G960" s="22"/>
+      <c r="E960" s="23"/>
+      <c r="G960" s="24"/>
     </row>
     <row r="961">
-      <c r="E961" s="21"/>
-      <c r="G961" s="22"/>
+      <c r="E961" s="23"/>
+      <c r="G961" s="24"/>
     </row>
     <row r="962">
-      <c r="E962" s="21"/>
-      <c r="G962" s="22"/>
+      <c r="E962" s="23"/>
+      <c r="G962" s="24"/>
     </row>
     <row r="963">
-      <c r="E963" s="21"/>
-      <c r="G963" s="22"/>
+      <c r="E963" s="23"/>
+      <c r="G963" s="24"/>
     </row>
     <row r="964">
-      <c r="E964" s="21"/>
-      <c r="G964" s="22"/>
+      <c r="E964" s="23"/>
+      <c r="G964" s="24"/>
     </row>
     <row r="965">
-      <c r="E965" s="21"/>
-      <c r="G965" s="22"/>
+      <c r="E965" s="23"/>
+      <c r="G965" s="24"/>
     </row>
     <row r="966">
-      <c r="E966" s="21"/>
-      <c r="G966" s="22"/>
+      <c r="E966" s="23"/>
+      <c r="G966" s="24"/>
     </row>
     <row r="967">
-      <c r="E967" s="21"/>
-      <c r="G967" s="22"/>
+      <c r="E967" s="23"/>
+      <c r="G967" s="24"/>
     </row>
     <row r="968">
-      <c r="E968" s="21"/>
-      <c r="G968" s="22"/>
+      <c r="E968" s="23"/>
+      <c r="G968" s="24"/>
     </row>
     <row r="969">
-      <c r="E969" s="21"/>
-      <c r="G969" s="22"/>
+      <c r="E969" s="23"/>
+      <c r="G969" s="24"/>
     </row>
     <row r="970">
-      <c r="E970" s="21"/>
-      <c r="G970" s="22"/>
+      <c r="E970" s="23"/>
+      <c r="G970" s="24"/>
     </row>
     <row r="971">
-      <c r="E971" s="21"/>
-      <c r="G971" s="22"/>
+      <c r="E971" s="23"/>
+      <c r="G971" s="24"/>
     </row>
     <row r="972">
-      <c r="E972" s="21"/>
-      <c r="G972" s="22"/>
+      <c r="E972" s="23"/>
+      <c r="G972" s="24"/>
     </row>
     <row r="973">
-      <c r="E973" s="21"/>
-      <c r="G973" s="22"/>
+      <c r="E973" s="23"/>
+      <c r="G973" s="24"/>
     </row>
     <row r="974">
-      <c r="E974" s="21"/>
-      <c r="G974" s="22"/>
+      <c r="E974" s="23"/>
+      <c r="G974" s="24"/>
     </row>
     <row r="975">
-      <c r="E975" s="21"/>
-      <c r="G975" s="22"/>
+      <c r="E975" s="23"/>
+      <c r="G975" s="24"/>
     </row>
     <row r="976">
-      <c r="E976" s="21"/>
-      <c r="G976" s="22"/>
+      <c r="E976" s="23"/>
+      <c r="G976" s="24"/>
     </row>
     <row r="977">
-      <c r="E977" s="21"/>
-      <c r="G977" s="22"/>
+      <c r="E977" s="23"/>
+      <c r="G977" s="24"/>
     </row>
     <row r="978">
-      <c r="E978" s="21"/>
-      <c r="G978" s="22"/>
+      <c r="E978" s="23"/>
+      <c r="G978" s="24"/>
     </row>
     <row r="979">
-      <c r="E979" s="21"/>
-      <c r="G979" s="22"/>
+      <c r="E979" s="23"/>
+      <c r="G979" s="24"/>
     </row>
     <row r="980">
-      <c r="E980" s="21"/>
-      <c r="G980" s="22"/>
+      <c r="E980" s="23"/>
+      <c r="G980" s="24"/>
     </row>
     <row r="981">
-      <c r="E981" s="21"/>
-      <c r="G981" s="22"/>
+      <c r="E981" s="23"/>
+      <c r="G981" s="24"/>
     </row>
     <row r="982">
-      <c r="E982" s="21"/>
-      <c r="G982" s="22"/>
+      <c r="E982" s="23"/>
+      <c r="G982" s="24"/>
     </row>
     <row r="983">
-      <c r="E983" s="21"/>
-      <c r="G983" s="22"/>
+      <c r="E983" s="23"/>
+      <c r="G983" s="24"/>
     </row>
     <row r="984">
-      <c r="E984" s="21"/>
-      <c r="G984" s="22"/>
+      <c r="E984" s="23"/>
+      <c r="G984" s="24"/>
     </row>
     <row r="985">
-      <c r="E985" s="21"/>
-      <c r="G985" s="22"/>
+      <c r="E985" s="23"/>
+      <c r="G985" s="24"/>
     </row>
     <row r="986">
-      <c r="E986" s="21"/>
-      <c r="G986" s="22"/>
+      <c r="E986" s="23"/>
+      <c r="G986" s="24"/>
     </row>
     <row r="987">
-      <c r="E987" s="21"/>
-      <c r="G987" s="22"/>
+      <c r="E987" s="23"/>
+      <c r="G987" s="24"/>
     </row>
     <row r="988">
-      <c r="E988" s="21"/>
-      <c r="G988" s="22"/>
+      <c r="E988" s="23"/>
+      <c r="G988" s="24"/>
     </row>
     <row r="989">
-      <c r="E989" s="21"/>
-      <c r="G989" s="22"/>
+      <c r="E989" s="23"/>
+      <c r="G989" s="24"/>
     </row>
     <row r="990">
-      <c r="E990" s="21"/>
-      <c r="G990" s="22"/>
+      <c r="E990" s="23"/>
+      <c r="G990" s="24"/>
     </row>
     <row r="991">
-      <c r="E991" s="21"/>
-      <c r="G991" s="22"/>
+      <c r="E991" s="23"/>
+      <c r="G991" s="24"/>
     </row>
     <row r="992">
-      <c r="E992" s="21"/>
-      <c r="G992" s="22"/>
+      <c r="E992" s="23"/>
+      <c r="G992" s="24"/>
     </row>
     <row r="993">
-      <c r="E993" s="21"/>
-      <c r="G993" s="22"/>
+      <c r="E993" s="23"/>
+      <c r="G993" s="24"/>
     </row>
     <row r="994">
-      <c r="E994" s="21"/>
-      <c r="G994" s="22"/>
+      <c r="E994" s="23"/>
+      <c r="G994" s="24"/>
     </row>
     <row r="995">
-      <c r="E995" s="21"/>
-      <c r="G995" s="22"/>
+      <c r="E995" s="23"/>
+      <c r="G995" s="24"/>
     </row>
     <row r="996">
-      <c r="E996" s="21"/>
-      <c r="G996" s="22"/>
+      <c r="E996" s="23"/>
+      <c r="G996" s="24"/>
     </row>
     <row r="997">
-      <c r="E997" s="21"/>
-      <c r="G997" s="22"/>
+      <c r="E997" s="23"/>
+      <c r="G997" s="24"/>
     </row>
     <row r="998">
-      <c r="E998" s="21"/>
-      <c r="G998" s="22"/>
+      <c r="E998" s="23"/>
+      <c r="G998" s="24"/>
     </row>
     <row r="999">
-      <c r="E999" s="21"/>
-      <c r="G999" s="22"/>
+      <c r="E999" s="23"/>
+      <c r="G999" s="24"/>
     </row>
     <row r="1000">
-      <c r="E1000" s="21"/>
-      <c r="G1000" s="22"/>
+      <c r="E1000" s="23"/>
+      <c r="G1000" s="24"/>
     </row>
     <row r="1001">
-      <c r="E1001" s="21"/>
-      <c r="G1001" s="22"/>
+      <c r="E1001" s="23"/>
+      <c r="G1001" s="24"/>
     </row>
     <row r="1002">
-      <c r="E1002" s="21"/>
-      <c r="G1002" s="22"/>
+      <c r="E1002" s="23"/>
+      <c r="G1002" s="24"/>
+    </row>
+    <row r="1003">
+      <c r="E1003" s="23"/>
+      <c r="G1003" s="24"/>
+    </row>
+    <row r="1004">
+      <c r="E1004" s="23"/>
+      <c r="G1004" s="24"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$H$117">
+  <autoFilter ref="$A$1:$H$119">
     <filterColumn colId="0">
       <filters>
         <filter val="2026년 6월"/>
@@ -7912,259 +8124,277 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="23" t="s">
+      <c r="B1" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="23" t="s">
+      <c r="D1" s="25" t="s">
         <v>65</v>
       </c>
+      <c r="E1" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="28">
         <v>2.164E7</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="29">
         <v>0.0329</v>
       </c>
-      <c r="E2" s="25">
+      <c r="E2" s="28">
         <f t="shared" ref="E2:E6" si="1">C2*D2/12</f>
         <v>59329.66667</v>
       </c>
+      <c r="F2" s="12" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="28">
         <v>1.0E8</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="29">
         <v>0.0349</v>
       </c>
-      <c r="E3" s="25">
+      <c r="E3" s="28">
         <f t="shared" si="1"/>
         <v>290833.3333</v>
       </c>
+      <c r="F3" s="12" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="28">
         <v>5.0E7</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="29">
         <v>0.0339</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="28">
         <f t="shared" si="1"/>
         <v>141250</v>
       </c>
+      <c r="F4" s="12" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="30">
         <v>6.5385014E7</v>
       </c>
-      <c r="D5" s="26">
-        <v>0.037</v>
-      </c>
-      <c r="E5" s="25">
+      <c r="D5" s="29">
+        <v>0.0512</v>
+      </c>
+      <c r="E5" s="28">
         <f t="shared" si="1"/>
-        <v>201603.7932</v>
+        <v>278976.0597</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="28">
         <v>1.12E8</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="29">
         <v>0.0339</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="28">
         <f t="shared" si="1"/>
         <v>316400</v>
       </c>
+      <c r="F6" s="32"/>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="25">
+      <c r="B7" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="28">
         <v>5.0E7</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="29">
         <v>0.05435</v>
       </c>
-      <c r="E7" s="29" t="s">
-        <v>28</v>
-      </c>
+      <c r="E7" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="32"/>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="32">
+      <c r="A8" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="36">
         <f>sum(C2:C6)</f>
         <v>349025014</v>
       </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="33">
+      <c r="D8" s="35"/>
+      <c r="E8" s="37">
         <f>sum(E2:E6)</f>
-        <v>1009416.793</v>
-      </c>
+        <v>1086789.06</v>
+      </c>
+      <c r="F8" s="38"/>
     </row>
     <row r="9">
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="36"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="41"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
     </row>
     <row r="10">
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="36"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="41"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
     </row>
     <row r="11">
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
     </row>
     <row r="12">
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
     </row>
     <row r="13">
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
     </row>
     <row r="14">
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
     </row>
     <row r="15">
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
     </row>
     <row r="16">
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
     </row>
     <row r="17">
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
     </row>
     <row r="19">
-      <c r="I19" s="34"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="36"/>
-      <c r="N19" s="35"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="43"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="40"/>
     </row>
     <row r="20">
-      <c r="I20" s="34"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="35"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="40"/>
     </row>
     <row r="21">
-      <c r="I21" s="34"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="35"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="40"/>
     </row>
     <row r="22">
-      <c r="I22" s="34"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="40"/>
-      <c r="N22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="44"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="44"/>
     </row>
     <row r="23">
-      <c r="I23" s="34"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="40"/>
-      <c r="N23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="44"/>
     </row>
     <row r="24">
-      <c r="I24" s="34"/>
-      <c r="J24" s="35"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="34"/>
-      <c r="M24" s="40"/>
-      <c r="N24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="44"/>
     </row>
     <row r="25">
-      <c r="I25" s="34"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="34"/>
-      <c r="M25" s="40"/>
-      <c r="N25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="44"/>
     </row>
     <row r="26">
-      <c r="I26" s="34"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="40"/>
-      <c r="N26" s="39"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="40"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="44"/>
     </row>
     <row r="27">
-      <c r="I27" s="34"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="34"/>
-      <c r="M27" s="40"/>
-      <c r="N27" s="39"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="40"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="39"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="44"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$E$8"/>
@@ -8184,6 +8414,7 @@
     <row r="3"/>
     <row r="4"/>
     <row r="5"/>
+    <row r="6"/>
   </sheetData>
   <drawing r:id="rId2"/>
 </worksheet>
